--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -9,15 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="+0.00%;-0.00%;0.00%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +34,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="000CA30C"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
+      <color rgb="00D03B3B"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +74,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -510,7 +548,241 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>523800</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>现价0.785高于50日均线0.608，EMA20与SAR均呈多头，T3形态突破。但RSI达72.25，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>30895100</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>2630400</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0065</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EFORCE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.97</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>606300</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:M6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,15 +89,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -556,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.785</v>
+        <v>0.39</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0397</v>
+        <v>0.0263</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>523800</v>
+        <v>9271000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.1</v>
+        <v>1.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.25</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -585,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.681</v>
+        <v>0.373</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.608</v>
+        <v>0.371</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -597,54 +598,62 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.785高于50日均线0.608，EMA20与SAR均呈多头，T3形态突破。但RSI达72.25，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.39高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破；RSI 66.85接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>30895100</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="H3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1586900</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 63.85未超买，信号技术面偏可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -654,40 +663,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2630400</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H4" t="n">
-        <v>85.84999999999999</v>
-      </c>
+        <v>251394100</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.178</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -699,39 +699,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E5" s="15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1050000</v>
+        <v>26942700</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="H5" t="n">
-        <v>63.97</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+        <v>51.85</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.196</v>
+        <v>0.025</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.171</v>
+        <v>0.024</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -744,45 +744,6360 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>606300</v>
+        <v>26672600</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>0.04</v>
       </c>
       <c r="H6" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+        <v>22.21</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.519</v>
+        <v>0.284</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.472</v>
+        <v>0.502</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>22413600</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>20309800</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H8" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>17256000</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>4.494</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>15315300</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>15208100</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7315</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AHB</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>14478400</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>13448000</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H13" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>12823700</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>10559200</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>10465100</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>10306700</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H17" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>9856300</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H18" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ICONIC</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>9816800</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H19" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>9332800</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H20" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>9110800</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H21" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0095</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>8538300</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>8301600</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>7862800</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H24" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>7160400</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78.73</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0303</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>7049700</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>-0.006500000000000001</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>6896000</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H27" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>6700800</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>6594000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HHRG</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>6104500</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H30" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>5960800</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H31" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>5923200</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H32" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>2.843</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>2.701</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>5868200</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>5841100</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>5682000</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>65.42</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.06950000000000001</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>5672400</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H36" t="n">
+        <v>63.03</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ENPRO</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>5443000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H37" t="n">
+        <v>95.37</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0065</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EFORCE</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>5393700</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H38" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>5003300</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H39" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0178</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SEDANIA</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>4974100</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H40" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>4827800</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>70.54000000000001</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>4758300</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H42" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>4400300</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H43" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>4296300</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H44" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>5.673</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>5.099</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>4171200</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H45" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>3614600</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>3566100</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H47" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7225</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>3560900</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H48" t="n">
+        <v>54.39</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>3546000</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H49" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>3319200</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H50" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>3239700</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H51" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>3209900</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H52" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0369</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>JSSOLAR</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>2948800</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="H53" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>2894700</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H54" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0.09570000000000001</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>2819700</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>2799000</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>2793500</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H57" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>3.484</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5230</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TUNEPRO</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>2753000</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H58" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>2733400</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>2720500</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>2705400</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H61" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>2576900</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H62" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0470</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BFIELD</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>2561000</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>2419900</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>82.13</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>2409300</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H65" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>2387500</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H66" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>2379900</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H67" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>2342100</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H68" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>2300100</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H69" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>2258300</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H70" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>-0.0331</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>2242700</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H71" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>2.096</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>-0.0308</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>2121500</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H72" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>3.435</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>2105500</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H73" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>4.598</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>4.539</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>2081100</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>2068000</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H75" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>2.191</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>1944200</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H76" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>1820700</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H77" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>2.854</v>
+      </c>
+      <c r="K77" s="9" t="n"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>1794700</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H78" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HIAPTEK</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>1757300</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H79" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>1746800</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H80" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>1677300</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H81" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0358</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ICTZONE</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>-0.0377</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>1656300</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H82" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>1653400</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H83" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TRC</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>1550900</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H84" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>1534600</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H85" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>1507800</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>1503200</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H87" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>1481600</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H88" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>1473100</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H89" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>1470100</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H90" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>WESTRVR</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>1398800</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H91" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>1384300</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>3.708</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>1374900</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H93" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>1322400</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H94" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>1292800</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>1282600</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H96" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0172</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OCK</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>1235200</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H97" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>9385</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LAYHONG</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>1211600</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H98" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>1201400</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H99" t="n">
+        <v>39</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>7.712</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0456</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MMCS</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>1177600</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0032</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>REDTONE</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>1150800</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H101" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>1149400</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>10.171</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>1148400</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H103" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>1142100</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H104" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>1117700</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H105" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>1097500</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H106" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>1081600</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H107" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>1075800</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H108" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>1046500</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H109" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>3.721</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>3.373</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>1041400</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H110" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>1026700</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1.651</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>1020700</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H112" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2.434</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>1000600</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H113" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>980200</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H114" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>970300</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H115" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>961500</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>13.506</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>14.083</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>960900</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H117" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>945500</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H118" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="I118" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>944400</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H119" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>939700</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H120" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>932600</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H121" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>924600</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H122" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>2.497</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>921900</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H123" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>1.856</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>878900</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H124" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>2.567</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>2.532</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>866900</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>4.746</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>4.584</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>848000</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H126" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>819800</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H127" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>775000</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="I128" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>743300</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H129" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>737300</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H130" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>723300</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H131" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>707900</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H132" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>3.272</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>702900</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H133" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>8.339</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>8.127000000000001</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H134" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>675800</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H135" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>661900</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H136" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>6.319</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>6.506</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>628400</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>620800</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>70</v>
+      </c>
+      <c r="I138" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>604800</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>595200</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H140" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>2.678</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>566200</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H141" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>5.732</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>EITA</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>558700</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H142" t="n">
+        <v>74.87</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>531200</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H143" t="n">
+        <v>36</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>3.311</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>3.497</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>517600</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H144" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>7.785</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>7.723</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>511300</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H145" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="I145" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>510300</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H146" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>506200</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H147" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.39</v>
+        <v>0.395</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0395</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9271000</v>
+        <v>12961000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.84999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.39高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破；RSI 66.85接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.395高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破。RSI 69.51接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -610,266 +610,315 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>0369</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>JSSOLAR</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>6199400</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>现价RM 0.25高于50日均线RM 0.197，EMA20与SAR均呈多头，T3形态突破。但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5667400</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>RSI 81.89已处超买区，现价高于50日均线约29.8%，EMA20与SAR多头信号虽一致，但短线过热。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>0455</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BUSCAP</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.555</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.0673</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>1586900</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="F5" s="5" t="n">
+        <v>2564800</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>63.85</v>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.493</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>0.395</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 63.85未超买，信号技术面偏可靠。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0041</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AIMAX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>251394100</v>
-      </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7079</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TWL</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>26942700</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.85偏强但未超买，信号技术面较可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>26672600</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H6" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1160600</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3形态突破；但RSI达73.56，已进入超买区，信号可靠性需留意短线过热。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VELESTO</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0217</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>22413600</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H7" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>20625800</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>现价0.84高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。但RSI达71.89，已进入超买区，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.008399999999999999</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>20309800</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H8" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1147100</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3突破有效；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -879,40 +928,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0083</v>
+        <v>0.015</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>17256000</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H9" t="n">
-        <v>59.08</v>
-      </c>
+        <v>253892200</v>
+      </c>
+      <c r="G9" s="12" t="n"/>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>4.494</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -924,39 +964,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.02</v>
+        <v>0.19</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15315300</v>
+        <v>50076000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H10" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.61</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.279</v>
+        <v>0.284</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.33</v>
+        <v>0.502</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,28 +1009,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.025</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15208100</v>
+        <v>27142700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.36</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>64.27</v>
+        <v>51.85</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
@@ -998,10 +1038,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.74</v>
+        <v>0.025</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1014,39 +1054,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14478400</v>
+        <v>24137800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="H12" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.72</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.053</v>
+        <v>0.241</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.043</v>
+        <v>0.25</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1059,39 +1099,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.305</v>
+        <v>4.83</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0469</v>
+        <v>-0.0021</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13448000</v>
+        <v>22991400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="H13" t="n">
-        <v>59.16</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.51</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.279</v>
+        <v>4.723</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.275</v>
+        <v>4.495</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1104,28 +1144,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12823700</v>
+        <v>20606100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H14" t="n">
-        <v>53.3</v>
+        <v>71.34</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -1133,10 +1173,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.231</v>
+        <v>0.543</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.232</v>
+        <v>0.491</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1149,28 +1189,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.475</v>
+        <v>0.24</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0104</v>
+        <v>-0.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10559200</v>
+        <v>17831100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="H15" t="n">
-        <v>52.83</v>
+        <v>30.84</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1178,10 +1218,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.468</v>
+        <v>0.279</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1194,28 +1234,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.84</v>
+        <v>0.785</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.0279</v>
+        <v>0.0064</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10465100</v>
+        <v>17341300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H16" t="n">
-        <v>64.33</v>
+        <v>64.27</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1223,10 +1263,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.725</v>
+        <v>0.74</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.51</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1239,28 +1279,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0.1271</v>
+        <v>0.155</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10306700</v>
+        <v>16073700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.31</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="n">
-        <v>95.67</v>
+        <v>44.71</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1268,10 +1308,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.841</v>
+        <v>0.156</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.722</v>
+        <v>0.16</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1284,39 +1324,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9856300</v>
+        <v>15444000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.62</v>
+        <v>0.95</v>
       </c>
       <c r="H18" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.04</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.132</v>
+        <v>0.28</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.059</v>
+        <v>0.275</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1329,39 +1369,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.095</v>
+        <v>2.1</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.0145</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9816800</v>
+        <v>14869000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.71</v>
+        <v>0.93</v>
       </c>
       <c r="H19" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.078</v>
+        <v>2.132</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.067</v>
+        <v>2.059</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1374,39 +1414,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.795</v>
+        <v>0.055</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9332800</v>
+        <v>14638400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.72</v>
+        <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1419,39 +1459,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>-0.0125</v>
+        <v>0.795</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9110800</v>
+        <v>13417000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="H21" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.314</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.178</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1464,28 +1504,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.09320000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8538300</v>
+        <v>13271900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.41</v>
+        <v>2.98</v>
       </c>
       <c r="H22" t="n">
-        <v>44.71</v>
+        <v>95.37</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1493,10 +1533,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.156</v>
+        <v>0.837</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.16</v>
+        <v>0.721</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1509,39 +1549,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8301600</v>
+        <v>13049300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H23" t="n">
-        <v>25.94</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.17</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.644</v>
+        <v>0.313</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.863</v>
+        <v>0.178</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1554,39 +1594,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.425</v>
+        <v>0.24</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.0241</v>
+        <v>0.0213</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7862800</v>
+        <v>12948100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>65.23999999999999</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.381</v>
+        <v>0.232</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.318</v>
+        <v>0.233</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1599,28 +1639,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.95</v>
+        <v>1.86</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0391</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7160400</v>
+        <v>12406900</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2.03</v>
+        <v>0.48</v>
       </c>
       <c r="H25" t="n">
-        <v>78.73</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
@@ -1628,10 +1668,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.878</v>
+        <v>1.727</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.85</v>
+        <v>1.511</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1644,39 +1684,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>-0.0303</v>
+        <v>-0.0435</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7049700</v>
+        <v>11968400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
-        <v>32.54</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.25</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0.183</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.224</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1689,28 +1729,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.765</v>
+        <v>0.31</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0159</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6896000</v>
+        <v>11685300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="n">
-        <v>45.47</v>
+        <v>59.8</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1718,10 +1758,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.773</v>
+        <v>0.303</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.774</v>
+        <v>0.29</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1734,28 +1774,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6700800</v>
+        <v>11520400</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="H28" t="n">
-        <v>71.51000000000001</v>
+        <v>50.88</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1763,10 +1803,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.142</v>
+        <v>0.468</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.114</v>
+        <v>0.47</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1779,39 +1819,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.775</v>
+        <v>0.53</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.0265</v>
+        <v>0.0095</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6594000</v>
+        <v>10958200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.27</v>
+        <v>0.28</v>
       </c>
       <c r="H29" t="n">
-        <v>71.29000000000001</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.92</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.68</v>
+        <v>0.645</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.608</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1824,28 +1864,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.095</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6104500</v>
+        <v>10111800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.15</v>
+        <v>1.77</v>
       </c>
       <c r="H30" t="n">
-        <v>49.56</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
@@ -1853,10 +1893,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.159</v>
+        <v>0.078</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.148</v>
+        <v>0.067</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1869,39 +1909,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>-0.0159</v>
+        <v>0.45</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5960800</v>
+        <v>9801000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.31</v>
+        <v>1.26</v>
       </c>
       <c r="H31" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.303</v>
+        <v>0.444</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.29</v>
+        <v>0.403</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1923,19 +1963,19 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0239</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5923200</v>
+        <v>9685400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="n">
-        <v>69.65000000000001</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -1943,10 +1983,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.843</v>
+        <v>2.848</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.701</v>
+        <v>2.702</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1959,39 +1999,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.36</v>
+        <v>0.765</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>-0.0216</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5868200</v>
+        <v>9656000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H33" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.47</v>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.384</v>
+        <v>0.773</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.288</v>
+        <v>0.774</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2004,33 +2044,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>2.85</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0.1004</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5841100</v>
+        <v>9558900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
+        <v>1.49</v>
+      </c>
+      <c r="H34" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>2.484</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
     </row>
@@ -2042,39 +2089,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.775</v>
+        <v>0.43</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0361</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5682000</v>
+        <v>8859800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="H35" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.08</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.698</v>
+        <v>0.381</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.318</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2087,28 +2134,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.865</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5672400</v>
+        <v>8816600</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.88</v>
+        <v>0.49</v>
       </c>
       <c r="H36" t="n">
-        <v>63.03</v>
+        <v>45.91</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
@@ -2116,10 +2163,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.599</v>
+        <v>0.868</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>2.483</v>
+        <v>0.871</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2132,39 +2179,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.165</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5443000</v>
+        <v>8459100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H37" t="n">
-        <v>95.37</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.262</v>
+        <v>0.183</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.218</v>
+        <v>0.224</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2177,28 +2224,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.225</v>
+        <v>0.76</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.0066</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5393700</v>
+        <v>8368700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.37</v>
+        <v>1.61</v>
       </c>
       <c r="H38" t="n">
-        <v>65.45</v>
+        <v>69.72</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2206,10 +2253,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.196</v>
+        <v>0.678</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.171</v>
+        <v>0.607</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2222,28 +2269,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>-0.0063</v>
+        <v>0.95</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0.027</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5003300</v>
+        <v>7831700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.48</v>
+        <v>2.22</v>
       </c>
       <c r="H39" t="n">
-        <v>47.18</v>
+        <v>78.73</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
@@ -2251,10 +2298,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.803</v>
+        <v>0.878</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.806</v>
+        <v>0.85</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2267,28 +2314,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4974100</v>
+        <v>7785600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="H40" t="n">
-        <v>54.5</v>
+        <v>44.21</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2296,10 +2343,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.103</v>
+        <v>0.197</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.096</v>
+        <v>0.196</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2312,39 +2359,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0.0169</v>
+        <v>1.33</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>-0.0432</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4827800</v>
+        <v>7619000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="H41" t="n">
-        <v>70.54000000000001</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.67</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.274</v>
+        <v>1.381</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.269</v>
+        <v>1.287</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2357,39 +2404,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.165</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4758300</v>
+        <v>7393400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.51000000000001</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.608</v>
+        <v>0.142</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.603</v>
+        <v>0.114</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2402,28 +2449,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.155</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4400300</v>
+        <v>6720100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.78</v>
+        <v>0.16</v>
       </c>
       <c r="H43" t="n">
-        <v>86.31</v>
+        <v>49.56</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2431,10 +2478,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.766</v>
+        <v>0.159</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.751</v>
+        <v>0.148</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2447,40 +2494,33 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.0138</v>
+        <v>0.265</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4296300</v>
+        <v>6681700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H44" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>5.673</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>5.099</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2492,28 +2532,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>2.39</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.0214</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4171200</v>
+        <v>6430600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>45.91</v>
+        <v>54.48</v>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
@@ -2521,10 +2561,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.868</v>
+        <v>2.348</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.871</v>
+        <v>2.232</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2537,28 +2577,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>0.0128</v>
+        <v>0.0172</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3614600</v>
+        <v>6282400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H46" t="n">
-        <v>53.14</v>
+        <v>63.7</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2566,10 +2606,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.346</v>
+        <v>5.675</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.231</v>
+        <v>5.1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2582,28 +2622,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>0.0452</v>
+        <v>0.0455</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3566100</v>
+        <v>6141000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>1.35</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>62.36</v>
+        <v>66.81</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2611,10 +2651,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.758</v>
+        <v>0.197</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.74</v>
+        <v>0.171</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2627,28 +2667,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.22</v>
+        <v>0.605</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0233</v>
+        <v>0.0168</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3560900</v>
+        <v>6007200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="H48" t="n">
-        <v>54.39</v>
+        <v>48.06</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2656,10 +2696,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.214</v>
+        <v>0.608</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.211</v>
+        <v>0.603</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2672,28 +2712,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.115</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3546000</v>
+        <v>5799300</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>54.08</v>
+        <v>48.46</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2701,10 +2741,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.444</v>
+        <v>0.119</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.403</v>
+        <v>0.106</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2717,28 +2757,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>-0.0133</v>
+        <v>0.785</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3319200</v>
+        <v>5695800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>52.41</v>
+        <v>86.31</v>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
@@ -2746,10 +2786,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.367</v>
+        <v>0.766</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.366</v>
+        <v>0.751</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2762,28 +2802,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.545</v>
+        <v>0.8</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.0323</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3239700</v>
+        <v>5522200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.22</v>
+        <v>2.09</v>
       </c>
       <c r="H51" t="n">
-        <v>69.40000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2791,10 +2831,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.467</v>
+        <v>0.757</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.397</v>
+        <v>0.74</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2807,28 +2847,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>-0.0086</v>
+        <v>0.335</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3209900</v>
+        <v>5512000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H52" t="n">
-        <v>46.5</v>
+        <v>95.37</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2836,10 +2876,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.181</v>
+        <v>0.262</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>1.135</v>
+        <v>0.218</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2852,28 +2892,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0.0667</v>
+        <v>0.295</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2948800</v>
+        <v>5082800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>4.97</v>
+        <v>0.84</v>
       </c>
       <c r="H53" t="n">
-        <v>68.40000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2881,10 +2921,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.206</v>
+        <v>0.273</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.197</v>
+        <v>0.269</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2897,28 +2937,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E54" s="16" t="n">
-        <v>-0.0187</v>
+        <v>0.805</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2894700</v>
+        <v>5026400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.36</v>
+        <v>1.49</v>
       </c>
       <c r="H54" t="n">
-        <v>79.89</v>
+        <v>49.91</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2926,10 +2966,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.876</v>
+        <v>0.804</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.752</v>
+        <v>0.806</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2942,39 +2982,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.26</v>
+        <v>0.105</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2819700</v>
+        <v>4983800</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>1.1</v>
       </c>
       <c r="H55" t="n">
-        <v>83.89</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.5</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.024</v>
+        <v>0.103</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.876</v>
+        <v>0.096</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2987,28 +3027,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>-0.0175</v>
+        <v>0.54</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0.0286</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2799000</v>
+        <v>4982500</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>58.3</v>
+        <v>68.8</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3016,10 +3056,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.086</v>
+        <v>0.466</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.023</v>
+        <v>0.397</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3032,28 +3072,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0.0513</v>
+        <v>1.04</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2793500</v>
+        <v>4372300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H57" t="n">
-        <v>78.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
@@ -3061,10 +3101,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.484</v>
+        <v>0.875</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>3.203</v>
+        <v>0.752</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3077,28 +3117,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>4.15</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0.0641</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2753000</v>
+        <v>4104700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>4.75</v>
+        <v>0.93</v>
       </c>
       <c r="H58" t="n">
-        <v>55.34</v>
+        <v>79.69</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3106,10 +3146,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.253</v>
+        <v>3.488</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.264</v>
+        <v>3.204</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3122,33 +3162,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.29</v>
+        <v>0.225</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0357</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2733400</v>
+        <v>4103400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
+        <v>0.67</v>
+      </c>
+      <c r="H59" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>0.211</v>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
     </row>
@@ -3160,28 +3207,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2720500</v>
+        <v>3990200</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H60" t="n">
-        <v>50.52</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3189,10 +3236,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.33</v>
+        <v>0.998</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.31</v>
+        <v>0.838</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3205,28 +3252,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0.06320000000000001</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2705400</v>
+        <v>3932600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.13</v>
+        <v>1.74</v>
       </c>
       <c r="H61" t="n">
-        <v>85.45</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3234,10 +3281,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.201</v>
+        <v>2.113</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.183</v>
+        <v>1.739</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3250,28 +3297,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0.0161</v>
+        <v>0.365</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2576900</v>
+        <v>3731900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="n">
-        <v>44.61</v>
+        <v>48.77</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3279,10 +3326,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.321</v>
+        <v>0.367</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.339</v>
+        <v>0.366</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3295,33 +3342,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0.0104</v>
+        <v>1.12</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2561000</v>
+        <v>3451900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
+      </c>
+      <c r="H63" t="n">
+        <v>58.3</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J63" s="9" t="n"/>
-      <c r="K63" s="9" t="n"/>
+      <c r="J63" s="9" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>1.023</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
@@ -3333,28 +3387,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0.0459</v>
+        <v>1.15</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2419900</v>
+        <v>3328100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="H64" t="n">
-        <v>82.13</v>
+        <v>46.5</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3362,10 +3416,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.999</v>
+        <v>1.181</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.838</v>
+        <v>1.135</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3378,40 +3432,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0.0189</v>
+        <v>0.48</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2409300</v>
+        <v>3324200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H65" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K65" s="9" t="n">
-        <v>0.473</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3423,39 +3470,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>-0.0077</v>
+        <v>0.535</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2387500</v>
+        <v>3292700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H66" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.16</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.332</v>
+        <v>0.519</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.452</v>
+        <v>0.473</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3468,39 +3515,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0.0208</v>
+        <v>3.44</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2379900</v>
+        <v>3259500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2.07</v>
+        <v>0.72</v>
       </c>
       <c r="H67" t="n">
-        <v>75.09</v>
-      </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.09</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.217</v>
+        <v>3.623</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.207</v>
+        <v>3.707</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3513,39 +3560,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0.052</v>
+        <v>0.77</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2342100</v>
+        <v>3146700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="H68" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.5</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.11</v>
+        <v>0.774</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.738</v>
+        <v>0.773</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3558,28 +3605,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0.09570000000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2300100</v>
+        <v>3077000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="H69" t="n">
-        <v>63.73</v>
+        <v>83.89</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3587,10 +3634,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.167</v>
+        <v>1.024</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.098</v>
+        <v>0.876</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3603,39 +3650,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>-0.0348</v>
+        <v>0.32</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2258300</v>
+        <v>3019600</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H70" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.222</v>
+        <v>0.321</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.099</v>
+        <v>0.339</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3648,28 +3695,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>-0.0331</v>
+        <v>0.335</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2242700</v>
+        <v>3010000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.39</v>
+        <v>0.95</v>
       </c>
       <c r="H71" t="n">
-        <v>73.29000000000001</v>
+        <v>48.96</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3677,10 +3724,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.429</v>
+        <v>0.335</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.096</v>
+        <v>0.342</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3693,39 +3740,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>4.4</v>
+        <v>2.21</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>-0.0308</v>
+        <v>-0.0391</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2121500</v>
+        <v>2993500</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H72" t="n">
-        <v>80.62</v>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.04</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.435</v>
+        <v>2.221</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.294</v>
+        <v>2.099</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3738,39 +3785,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0218</v>
+        <v>2.48</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2105500</v>
+        <v>2962100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="H73" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>4.598</v>
+        <v>2.434</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>4.539</v>
+        <v>2.267</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3783,40 +3830,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.295</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2081100</v>
+        <v>2943600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H74" t="n">
-        <v>40.8</v>
+        <v>0.13</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J74" s="9" t="n">
-        <v>4.851</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>4.967</v>
-      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3828,28 +3868,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.0833</v>
+        <v>1.29</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2068000</v>
+        <v>2924600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1.09</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>89.28</v>
+        <v>33.75</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3857,10 +3897,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.191</v>
+        <v>1.332</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.93</v>
+        <v>1.452</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3873,39 +3913,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.905</v>
+        <v>0.33</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>0.0169</v>
+        <v>0.0154</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1944200</v>
+        <v>2908400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.57</v>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.929</v>
+        <v>0.331</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.969</v>
+        <v>0.31</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3918,38 +3958,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>-0.0135</v>
+        <v>0.605</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1820700</v>
+        <v>2777300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.16</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="K77" s="9" t="n"/>
+        <v>0.64</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0.658</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
     </row>
@@ -3961,28 +4003,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>0.0148</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1794700</v>
+        <v>2777200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.17</v>
+        <v>1.09</v>
       </c>
       <c r="H78" t="n">
-        <v>51.73</v>
+        <v>41.51</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -3990,10 +4032,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.677</v>
+        <v>1.587</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.66</v>
+        <v>1.65</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4006,28 +4048,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0.0392</v>
+        <v>0.26</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1757300</v>
+        <v>2762200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.35</v>
+        <v>4.76</v>
       </c>
       <c r="H79" t="n">
-        <v>59.89</v>
+        <v>55.34</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4035,10 +4077,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.257</v>
+        <v>0.253</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.259</v>
+        <v>0.264</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4051,39 +4093,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0.0278</v>
+        <v>0.265</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1746800</v>
+        <v>2733700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="H80" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.13</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.96</v>
+        <v>0.262</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4096,39 +4138,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1677300</v>
+        <v>2732700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H81" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.166</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.592</v>
+        <v>1.098</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4141,39 +4183,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>-0.0377</v>
+        <v>2.88</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1656300</v>
+        <v>2688800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.53</v>
+        <v>1.42</v>
       </c>
       <c r="H82" t="n">
-        <v>48.14</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.48999999999999</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.261</v>
+        <v>2.193</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.25</v>
+        <v>1.931</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4186,39 +4228,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0383</v>
+        <v>0.0112</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1653400</v>
+        <v>2668600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="H83" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="I83" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.888</v>
+        <v>0.928</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.801</v>
+        <v>0.969</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4231,39 +4273,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>0.0492</v>
+        <v>4.49</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1550900</v>
+        <v>2657800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.88</v>
+        <v>0.35</v>
       </c>
       <c r="H84" t="n">
-        <v>71.23</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.1</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.297</v>
+        <v>4.599</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.28</v>
+        <v>4.54</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4276,28 +4318,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>0.0233</v>
+        <v>4.44</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1534600</v>
+        <v>2627400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>59.78</v>
+        <v>82.14</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4305,10 +4347,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.63</v>
+        <v>3.438</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.571</v>
+        <v>2.295</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4321,39 +4363,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.0204</v>
+        <v>4.8</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1507800</v>
+        <v>2522300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="H86" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.477</v>
+        <v>4.851</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.536</v>
+        <v>4.967</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4366,28 +4408,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
+        <v>0.965</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-0.0446</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1503200</v>
+        <v>2439500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>46.56</v>
+        <v>36.63</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4395,10 +4437,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.295</v>
+        <v>1.053</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.297</v>
+        <v>1.011</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4411,40 +4453,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.38</v>
+        <v>2.93</v>
       </c>
       <c r="E88" s="16" t="n">
-        <v>-0.035</v>
+        <v>-0.0135</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1481600</v>
+        <v>2428200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="H88" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.48</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.416</v>
-      </c>
-      <c r="K88" s="9" t="n">
-        <v>1.315</v>
-      </c>
+        <v>2.854</v>
+      </c>
+      <c r="K88" s="9" t="n"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
@@ -4456,39 +4496,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1473100</v>
+        <v>2379200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H89" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.859</v>
+        <v>0.96</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.856</v>
+        <v>0.79</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4501,39 +4541,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1470100</v>
+        <v>2346200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H90" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.78</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.658</v>
+        <v>0.571</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4546,28 +4586,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0122</v>
+        <v>0.59</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1398800</v>
+        <v>2331300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H91" t="n">
-        <v>70.53</v>
+        <v>47.34</v>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
@@ -4575,10 +4615,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.368</v>
+        <v>0.592</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.336</v>
+        <v>0.611</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4591,28 +4631,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>3.48</v>
+        <v>2.62</v>
       </c>
       <c r="E92" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0368</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1384300</v>
+        <v>2296000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H92" t="n">
-        <v>36.11</v>
+        <v>72.16</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4620,10 +4660,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>3.627</v>
+        <v>2.428</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>3.708</v>
+        <v>2.096</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4636,39 +4676,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1374900</v>
+        <v>2276100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>58.41</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.96</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.408</v>
+        <v>1.742</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.409</v>
+        <v>1.856</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4681,28 +4721,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0272</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1322400</v>
+        <v>2238400</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.38</v>
+        <v>0.89</v>
       </c>
       <c r="H94" t="n">
-        <v>70.44</v>
+        <v>54.82</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4710,10 +4750,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.099</v>
+        <v>1.478</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.999</v>
+        <v>1.536</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4726,33 +4766,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>-0.0169</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0.0148</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1292800</v>
+        <v>2152400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
+      </c>
+      <c r="H95" t="n">
+        <v>51.73</v>
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="J95" s="9" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0.66</v>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4764,39 +4811,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0.0244</v>
+        <v>0.0492</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1282600</v>
+        <v>2120000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
       <c r="H96" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.88</v>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.614</v>
+        <v>0.889</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.579</v>
+        <v>0.802</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4809,28 +4856,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>-0.0102</v>
+        <v>0.26</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1235200</v>
+        <v>2110300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="H97" t="n">
-        <v>71.70999999999999</v>
+        <v>39.54</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4838,10 +4885,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.442</v>
+        <v>0.274</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.402</v>
+        <v>0.316</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4854,39 +4901,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1211600</v>
+        <v>2017700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>2.09</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.247</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.244</v>
+        <v>0.592</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4899,39 +4946,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0.0054</v>
+        <v>0.31</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1201400</v>
+        <v>1761000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H99" t="n">
-        <v>39</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.25</v>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>7.712</v>
+        <v>0.307</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>7.854</v>
+        <v>0.294</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4944,39 +4991,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1177600</v>
+        <v>1760100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="H100" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.365</v>
+        <v>0.257</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.395</v>
+        <v>0.259</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4989,39 +5036,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.027</v>
+        <v>1</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1150800</v>
+        <v>1760000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.73</v>
+        <v>0.35</v>
       </c>
       <c r="H101" t="n">
-        <v>60.24</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.5</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.352</v>
+        <v>1.053</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.318</v>
+        <v>1.073</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5034,39 +5081,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>10.16</v>
+        <v>0.775</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>0.004</v>
+        <v>0.0265</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1149400</v>
+        <v>1759300</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H102" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.81</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>10.171</v>
+        <v>0.799</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>10.334</v>
+        <v>0.853</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5079,28 +5126,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.62</v>
+        <v>0.42</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>0.0038</v>
+        <v>0.012</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1148400</v>
+        <v>1707700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H103" t="n">
-        <v>55.6</v>
+        <v>62.57</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5108,10 +5155,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.587</v>
+        <v>0.408</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.433</v>
+        <v>0.409</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5124,39 +5171,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1142100</v>
+        <v>1697900</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
       <c r="H104" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.53</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.774</v>
+        <v>0.368</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.773</v>
+        <v>0.336</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5169,28 +5216,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0.02</v>
+        <v>1.38</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.035</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1117700</v>
+        <v>1668500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.22</v>
+        <v>0.73</v>
       </c>
       <c r="H105" t="n">
-        <v>38.46</v>
+        <v>47.07</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5198,10 +5245,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.055</v>
+        <v>1.416</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.073</v>
+        <v>1.315</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5214,39 +5261,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0.0325</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1097500</v>
+        <v>1622600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H106" t="n">
-        <v>55.46</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.73</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.399</v>
+        <v>0.614</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.398</v>
+        <v>0.579</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5259,39 +5306,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>0.0286</v>
+        <v>4.77</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1081600</v>
+        <v>1617000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.334</v>
+        <v>4.746</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.318</v>
+        <v>4.584</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5304,28 +5351,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>2.63</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1075800</v>
+        <v>1603500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="H108" t="n">
-        <v>49.25</v>
+        <v>56.31</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5333,10 +5380,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.989</v>
+        <v>2.588</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.976</v>
+        <v>2.433</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5349,28 +5396,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3.96</v>
+        <v>1.19</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.0154</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1046500</v>
+        <v>1599500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H109" t="n">
-        <v>66.63</v>
+        <v>70.44</v>
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
@@ -5378,10 +5425,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>3.721</v>
+        <v>1.099</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>3.373</v>
+        <v>0.999</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5403,19 +5450,19 @@
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1041400</v>
+        <v>1586800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="H110" t="n">
-        <v>41.59</v>
+        <v>44.16</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5423,7 +5470,7 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0.753</v>
@@ -5439,28 +5486,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.7</v>
+        <v>0.485</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>-0.0173</v>
+        <v>-0.0102</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1026700</v>
+        <v>1579500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.3</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>54.71</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
@@ -5468,10 +5515,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.651</v>
+        <v>0.442</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.727</v>
+        <v>0.402</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5484,28 +5531,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>2.48</v>
+        <v>4.01</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0282</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1020700</v>
+        <v>1567200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="n">
-        <v>59.9</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
@@ -5513,10 +5560,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2.434</v>
+        <v>3.726</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.267</v>
+        <v>3.374</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5529,28 +5576,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.655</v>
+        <v>0.32</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>0.0077</v>
+        <v>0.0492</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1000600</v>
+        <v>1552000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.29</v>
+        <v>1.88</v>
       </c>
       <c r="H113" t="n">
-        <v>72.5</v>
+        <v>71.23</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5558,10 +5605,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.633</v>
+        <v>0.297</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.589</v>
+        <v>0.28</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5574,39 +5621,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0.0108</v>
+        <v>2.58</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>980200</v>
+        <v>1538900</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H114" t="n">
-        <v>59.15</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.82</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.906</v>
+        <v>2.68</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.776</v>
+        <v>2.796</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5619,28 +5666,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.89</v>
+        <v>3.54</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.0381</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>970300</v>
+        <v>1521100</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.21</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>36.12</v>
+        <v>73.88</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5648,10 +5695,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.964</v>
+        <v>3.272</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.085</v>
+        <v>2.859</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5664,39 +5711,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0.0123</v>
+        <v>0.295</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>961500</v>
+        <v>1503200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.1</v>
+        <v>0.97</v>
       </c>
       <c r="H116" t="n">
-        <v>34.04</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.56</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>13.506</v>
+        <v>0.295</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>14.083</v>
+        <v>0.297</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5709,39 +5756,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0.0199</v>
+        <v>6.25</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>960900</v>
+        <v>1492700</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H117" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.59</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.799</v>
+        <v>6.319</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.852</v>
+        <v>6.506</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5754,28 +5801,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>1.98</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>945500</v>
+        <v>1479100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H118" t="n">
-        <v>58.87</v>
+        <v>49.25</v>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
@@ -5783,10 +5830,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.512</v>
+        <v>1.989</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.461</v>
+        <v>1.976</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5799,39 +5846,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0116</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>944400</v>
+        <v>1476600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.39</v>
+        <v>1.87</v>
       </c>
       <c r="H119" t="n">
-        <v>40.92</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.056</v>
+        <v>1.652</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.011</v>
+        <v>1.727</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5844,39 +5891,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>1476100</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H120" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="K120" s="9" t="n">
         <v>0.855</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="F120" s="11" t="n">
-        <v>939700</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H120" t="n">
-        <v>67.06</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>0.714</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5889,39 +5936,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>-0.0038</v>
+        <v>10.14</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0.002</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>932600</v>
+        <v>1468200</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.29</v>
+        <v>0.08</v>
       </c>
       <c r="H121" t="n">
-        <v>32.71</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.681</v>
+        <v>10.17</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.796</v>
+        <v>10.333</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5934,40 +5981,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0.0121</v>
+        <v>0.295</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>924600</v>
+        <v>1453200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H122" t="n">
-        <v>78.84</v>
+        <v>0.08</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J122" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K122" s="9" t="n">
-        <v>2.497</v>
-      </c>
+      <c r="J122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -5979,39 +6019,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>-0.012</v>
+        <v>13.22</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>921900</v>
+        <v>1449800</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H123" t="n">
-        <v>31.96</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.04</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.742</v>
+        <v>13.506</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.856</v>
+        <v>14.083</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6024,28 +6064,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E124" s="17" t="n">
-        <v>0.0117</v>
+        <v>0.41</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>878900</v>
+        <v>1429200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="H124" t="n">
-        <v>53.03</v>
+        <v>53.93</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6053,10 +6093,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>2.567</v>
+        <v>0.399</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.532</v>
+        <v>0.398</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6069,28 +6109,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0</v>
+        <v>7.47</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>866900</v>
+        <v>1418800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>56.74</v>
+        <v>37.48</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6098,10 +6138,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>4.746</v>
+        <v>7.709</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>4.584</v>
+        <v>7.853</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6114,39 +6154,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.575</v>
+        <v>0.36</v>
       </c>
       <c r="E126" s="17" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0286</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>848000</v>
+        <v>1400400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H126" t="n">
-        <v>41.22</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.7</v>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.591</v>
+        <v>0.334</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.611</v>
+        <v>0.318</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6159,39 +6199,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.4</v>
+        <v>0.945</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0216</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>819800</v>
+        <v>1348500</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="H127" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.38</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.341</v>
+        <v>0.907</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.138</v>
+        <v>0.776</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6204,39 +6244,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>775000</v>
+        <v>1292300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H128" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="I128" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.55</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.587</v>
+        <v>1.292</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.65</v>
+        <v>1.324</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6249,28 +6289,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>743300</v>
+        <v>1284300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>48.52</v>
+        <v>53.62</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6278,10 +6318,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>3.012</v>
+        <v>0.351</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.04</v>
+        <v>0.318</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6294,39 +6334,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E130" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.525</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>737300</v>
+        <v>1259900</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H130" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.8</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.633</v>
+        <v>0.518</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.628</v>
+        <v>0.53</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6339,28 +6379,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.89</v>
+        <v>2.4</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.0573</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>723300</v>
+        <v>1258300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="H131" t="n">
-        <v>72.90000000000001</v>
+        <v>68.12</v>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
@@ -6368,10 +6408,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.197</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.794</v>
+        <v>2.016</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6384,28 +6424,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.58</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>707900</v>
+        <v>1256800</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H132" t="n">
-        <v>73.88</v>
+        <v>43.05</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6413,10 +6453,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>3.272</v>
+        <v>0.588</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>2.859</v>
+        <v>0.587</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6429,28 +6469,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.84</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>702900</v>
+        <v>1255900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>2.36</v>
+        <v>0.44</v>
       </c>
       <c r="H133" t="n">
-        <v>61.01</v>
+        <v>64.22</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6458,10 +6498,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>8.339</v>
+        <v>0.797</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6474,39 +6514,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.63</v>
+        <v>0.205</v>
       </c>
       <c r="E134" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>700000</v>
+        <v>1233800</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H134" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.631</v>
+        <v>0.199</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.637</v>
+        <v>0.206</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6519,28 +6559,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.27</v>
+        <v>1.89</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>675800</v>
+        <v>1230700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="H135" t="n">
-        <v>41.55</v>
+        <v>36.12</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6548,10 +6588,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.292</v>
+        <v>1.964</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.324</v>
+        <v>2.085</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6564,28 +6604,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>6.25</v>
+        <v>0.25</v>
       </c>
       <c r="E136" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>661900</v>
+        <v>1223600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.04</v>
+        <v>2.11</v>
       </c>
       <c r="H136" t="n">
-        <v>42.59</v>
+        <v>55.11</v>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
@@ -6593,10 +6633,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>6.319</v>
+        <v>0.247</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>6.506</v>
+        <v>0.244</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6609,28 +6649,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.53</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>628400</v>
+        <v>1220900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H137" t="n">
-        <v>49.13</v>
+        <v>58.87</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6638,10 +6678,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.771</v>
+        <v>0.512</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.807</v>
+        <v>0.461</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6654,28 +6694,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.73</v>
+        <v>3.34</v>
       </c>
       <c r="E138" s="17" t="n">
-        <v>0.021</v>
+        <v>0.0091</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>620800</v>
+        <v>1211700</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="H138" t="n">
-        <v>70</v>
+        <v>78.62</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6683,10 +6723,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.667</v>
+        <v>2.909</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.61</v>
+        <v>2.497</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6699,28 +6739,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0</v>
+        <v>1.76</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>604800</v>
+        <v>1194100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H139" t="n">
-        <v>50.49</v>
+        <v>47.91</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6728,10 +6768,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.517</v>
+        <v>1.77</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.53</v>
+        <v>1.807</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6744,39 +6784,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.0037</v>
+        <v>0.36</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>595200</v>
+        <v>1181600</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.39</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.678</v>
+        <v>0.365</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.883</v>
+        <v>0.395</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6789,39 +6829,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5.77</v>
+        <v>2.99</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0069</v>
+        <v>-0.0033</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>566200</v>
+        <v>1159100</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H141" t="n">
-        <v>49.54</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I141" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>5.81</v>
+        <v>3.011</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>5.732</v>
+        <v>3.04</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6834,39 +6874,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>0.0274</v>
+        <v>1.88</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>558700</v>
+        <v>1142600</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>4.39</v>
+        <v>0.17</v>
       </c>
       <c r="H142" t="n">
-        <v>74.87</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.19</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.672</v>
+        <v>1.92</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.609</v>
+        <v>1.971</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6879,28 +6919,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>3.21</v>
+        <v>0.615</v>
       </c>
       <c r="E143" s="17" t="n">
-        <v>0.0031</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>531200</v>
+        <v>1091800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.15</v>
+        <v>0.37</v>
       </c>
       <c r="H143" t="n">
-        <v>36</v>
+        <v>65.06</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -6908,10 +6948,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>3.311</v>
+        <v>0.608</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>3.497</v>
+        <v>0.587</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6924,28 +6964,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="E144" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>2.58</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>517600</v>
+        <v>1077600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H144" t="n">
-        <v>57.19</v>
+        <v>51.98</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6953,10 +6993,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>7.785</v>
+        <v>2.566</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>7.723</v>
+        <v>2.532</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6969,28 +7009,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0</v>
+        <v>0.655</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>511300</v>
+        <v>1055900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H145" t="n">
-        <v>57.39</v>
+        <v>72.5</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -6998,10 +7038,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.569</v>
+        <v>0.633</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.574</v>
+        <v>0.589</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7014,28 +7054,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E146" s="16" t="n">
-        <v>-0.0052</v>
+        <v>1.4</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>510300</v>
+        <v>1021300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="H146" t="n">
-        <v>45.64</v>
+        <v>60.62</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7043,10 +7083,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.922</v>
+        <v>1.341</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.971</v>
+        <v>1.138</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7059,28 +7099,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.99</v>
+        <v>0.74</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0258</v>
+        <v>0.035</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>506200</v>
+        <v>1001300</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H147" t="n">
-        <v>52.13</v>
+        <v>71.39</v>
       </c>
       <c r="I147" s="15" t="inlineStr">
         <is>
@@ -7088,16 +7128,1501 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.964</v>
+        <v>0.668</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.026</v>
+        <v>0.61</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>939100</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>5.808</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>5.731</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>901200</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H149" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>867300</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H150" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>857200</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H151" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>7.784</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>7.723</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>826300</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H152" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>817700</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H153" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>2.884</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>809700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H154" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="I154" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>756400</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H155" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>748500</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="I156" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>7.652</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>7.801</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>745500</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H157" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>3.309</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>3.497</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>718100</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H158" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>UMSINT</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>702900</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H159" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="I159" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>8.339</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>8.127000000000001</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H160" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>686000</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H161" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="I161" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>660400</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H162" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>658400</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>646600</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H164" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="I164" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>2.673</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>8206</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ECOWLD</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>637400</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H165" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="I165" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>631600</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H166" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="I166" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>7.992</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>8.272</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>625700</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H167" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EITA</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>621100</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="H168" t="n">
+        <v>74.87</v>
+      </c>
+      <c r="I168" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>615200</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H169" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>598700</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H170" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="I170" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>597800</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H171" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>596300</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H172" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>7.791</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>588300</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H173" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="I173" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>4.742</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>5.008</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H174" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>581400</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H175" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>581400</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H176" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>3.081</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>564600</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H177" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>5.722</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>6.099</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>525300</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>5.035</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>505100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H179" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>8.689</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>8.548999999999999</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>501400</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H180" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0395</v>
+        <v>0.0263</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>12961000</v>
+        <v>14778000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.51000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.395高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破。RSI 69.51接近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.39高于50日均线0.371，EMA20与SAR均呈多头，T3形态突破；RSI 66.85接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6199400</v>
+        <v>6696600</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>10.45</v>
+        <v>11.29</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.13</v>
+        <v>69.83</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价RM 0.25高于50日均线RM 0.197，EMA20与SAR均呈多头，T3形态突破。但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3突破信号偏强；但RSI达69.83，接近超买区，可靠性略受抑制。</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>0.125</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>5667400</v>
+        <v>7372200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4.93</v>
+        <v>6.42</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>81.89</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>RSI 81.89已处超买区，现价高于50日均线约29.8%，EMA20与SAR多头信号虽一致，但短线过热。</t>
+          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头排列，T3突破信号偏强，但超买或加大回调风险。</t>
         </is>
       </c>
     </row>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.555</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0673</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2564800</v>
+        <v>2748400</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>63.85</v>
+        <v>64.42</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.395</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.555高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.85偏强但未超买，信号技术面较可靠。</t>
+          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 64.42接近超买区但未破70，信号偏强。</t>
         </is>
       </c>
     </row>
@@ -784,10 +784,10 @@
         <v>0.017</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1160600</v>
+        <v>1244100</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>73.56</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3形态突破；但RSI达73.56，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3突破有效；但RSI达73.56，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.84</v>
+        <v>0.865</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1234</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>20625800</v>
+        <v>23676300</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.89</v>
+        <v>73.77</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.704</v>
+        <v>0.707</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.84高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。但RSI达71.89，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.865高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达73.77，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -890,10 +890,10 @@
         <v>0.0217</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1147100</v>
+        <v>1322500</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>72.40000000000001</v>
@@ -916,7 +916,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3突破有效；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>253892200</v>
+        <v>257407400</v>
       </c>
       <c r="G9" s="12" t="n"/>
       <c r="I9" s="13" t="inlineStr">
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>50076000</v>
+        <v>50531300</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0.08</v>
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.0217</v>
+        <v>-0.0435</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>24137800</v>
+        <v>26044400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="H12" t="n">
-        <v>34.72</v>
+        <v>32.28</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0021</v>
+        <v>4.85</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>22991400</v>
+        <v>24416900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="H13" t="n">
-        <v>61.51</v>
+        <v>62.88</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>4.723</v>
+        <v>4.725</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>4.495</v>
@@ -1159,10 +1159,10 @@
         <v>-0.0168</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>20606100</v>
+        <v>24215700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="H14" t="n">
         <v>71.34</v>
@@ -1204,10 +1204,10 @@
         <v>-0.04</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>17831100</v>
+        <v>22800200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="n">
         <v>30.84</v>
@@ -1234,28 +1234,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.385</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>-0.0375</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>17341300</v>
+        <v>18156300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H16" t="n">
-        <v>64.27</v>
+        <v>79.02</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.74</v>
+        <v>0.313</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.178</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1279,28 +1279,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.155</v>
+        <v>0.78</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>16073700</v>
+        <v>17841500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="n">
-        <v>44.71</v>
+        <v>63.44</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.156</v>
+        <v>0.739</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.16</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         <v>-0.0313</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>15444000</v>
+        <v>16585700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H18" t="n">
         <v>61.04</v>
@@ -1369,39 +1369,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.155</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>14869000</v>
+        <v>16073700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="H19" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.71</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2.132</v>
+        <v>0.156</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>2.059</v>
+        <v>0.16</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>14638400</v>
+        <v>15511400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="H20" t="n">
         <v>56.29</v>
@@ -1459,28 +1459,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>13417000</v>
+        <v>15258800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="H21" t="n">
-        <v>42.35</v>
+        <v>48.11</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.132</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.059</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>13271900</v>
+        <v>14871200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2.98</v>
+        <v>3.33</v>
       </c>
       <c r="H22" t="n">
         <v>95.37</v>
@@ -1549,28 +1549,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-0.025</v>
+        <v>-0.0159</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13049300</v>
+        <v>13943300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="H23" t="n">
-        <v>81.17</v>
+        <v>59.8</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.313</v>
+        <v>0.303</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.178</v>
+        <v>0.29</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1594,28 +1594,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.24</v>
+        <v>1.86</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.0213</v>
+        <v>0.0391</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>12948100</v>
+        <v>13605700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
-        <v>56.19</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.232</v>
+        <v>1.727</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.233</v>
+        <v>1.511</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1639,39 +1639,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.795</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>12406900</v>
+        <v>13431000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.48</v>
+        <v>1.03</v>
       </c>
       <c r="H25" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.727</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.511</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.0435</v>
+        <v>0.24</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>11968400</v>
+        <v>13072100</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>71.25</v>
+        <v>56.19</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.2</v>
+        <v>0.232</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.183</v>
+        <v>0.233</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1729,28 +1729,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.0159</v>
+        <v>-0.0435</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>11685300</v>
+        <v>12776000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H27" t="n">
-        <v>59.8</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.303</v>
+        <v>0.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.29</v>
+        <v>0.183</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1774,28 +1774,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>-0.0208</v>
+        <v>3.06</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>11520400</v>
+        <v>11601700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.46</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="n">
-        <v>50.88</v>
+        <v>72.83</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.468</v>
+        <v>2.848</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.47</v>
+        <v>2.702</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1819,39 +1819,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0.0095</v>
+        <v>0.475</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>10958200</v>
+        <v>11581700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H29" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.83</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.645</v>
+        <v>0.468</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.863</v>
+        <v>0.47</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1864,39 +1864,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.52</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>10111800</v>
+        <v>11428500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.77</v>
+        <v>0.29</v>
       </c>
       <c r="H30" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.6</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.078</v>
+        <v>0.644</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.067</v>
+        <v>0.863</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1909,39 +1909,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9801000</v>
+        <v>11049200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.26</v>
+        <v>0.62</v>
       </c>
       <c r="H31" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.444</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.403</v>
+        <v>0.871</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3.05</v>
+        <v>0.45</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0227</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>9685400</v>
+        <v>10633600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.77</v>
+        <v>1.37</v>
       </c>
       <c r="H32" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.848</v>
+        <v>0.444</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.702</v>
+        <v>0.403</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>2.87</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.1081</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9656000</v>
+        <v>10445500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.8</v>
+        <v>1.63</v>
       </c>
       <c r="H33" t="n">
-        <v>45.47</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.773</v>
+        <v>2.608</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.774</v>
+        <v>2.485</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2044,28 +2044,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.85</v>
+        <v>0.095</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.1004</v>
+        <v>0.0556</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>9558900</v>
+        <v>10111800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="H34" t="n">
-        <v>66.36</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.606</v>
+        <v>0.078</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.484</v>
+        <v>0.067</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2089,39 +2089,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0.0361</v>
+        <v>0.76</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>8859800</v>
+        <v>9936400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="H35" t="n">
-        <v>66.08</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.44</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.381</v>
+        <v>0.773</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.318</v>
+        <v>0.774</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2134,39 +2134,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.43</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>8816600</v>
+        <v>9039400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H36" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.08</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.868</v>
+        <v>0.381</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.871</v>
+        <v>0.318</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8459100</v>
+        <v>8898100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H37" t="n">
         <v>34.16</v>
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.76</v>
+        <v>0.765</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0066</v>
+        <v>0.0132</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>8368700</v>
+        <v>8587000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H38" t="n">
-        <v>69.72</v>
+        <v>70.27</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.678</v>
+        <v>0.679</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0.607</v>
@@ -2269,39 +2269,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0.027</v>
+        <v>1.33</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>-0.0432</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7831700</v>
+        <v>8551500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>2.22</v>
+        <v>0.73</v>
       </c>
       <c r="H39" t="n">
-        <v>78.73</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.67</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.878</v>
+        <v>1.381</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.85</v>
+        <v>1.287</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2314,39 +2314,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>0.955</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0.03240000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>7785600</v>
+        <v>8459500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.95</v>
+        <v>2.39</v>
       </c>
       <c r="H40" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.42</v>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.197</v>
+        <v>0.878</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.196</v>
+        <v>0.85</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2359,28 +2359,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>-0.0432</v>
+        <v>0.19</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7619000</v>
+        <v>8069100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="H41" t="n">
-        <v>45.67</v>
+        <v>44.21</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.381</v>
+        <v>0.197</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.287</v>
+        <v>0.196</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2404,28 +2404,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>5.9</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7393400</v>
+        <v>7939100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H42" t="n">
-        <v>71.51000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.142</v>
+        <v>5.675</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.114</v>
+        <v>5.1</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2449,28 +2449,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.17</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6720100</v>
+        <v>7776300</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>49.56</v>
+        <v>73.31</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.159</v>
+        <v>0.142</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.148</v>
+        <v>0.114</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2494,33 +2494,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>-0.0185</v>
+        <v>2.41</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6681700</v>
+        <v>7773600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
+        <v>0.44</v>
+      </c>
+      <c r="H44" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>2.232</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2532,40 +2539,33 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0.0214</v>
+        <v>0.265</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6430600</v>
+        <v>6815700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H45" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>2.348</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>2.232</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
     </row>
@@ -2577,28 +2577,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.0172</v>
+        <v>0.155</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6282400</v>
+        <v>6756800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
-        <v>63.7</v>
+        <v>49.56</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>5.675</v>
+        <v>0.159</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>5.1</v>
+        <v>0.148</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2622,39 +2622,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0.0455</v>
+        <v>0.115</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>6141000</v>
+        <v>6314300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.197</v>
+        <v>0.119</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.171</v>
+        <v>0.106</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2667,39 +2667,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.605</v>
+        <v>0.235</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.0682</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>6007200</v>
+        <v>6143500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="H48" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.06</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.608</v>
+        <v>0.197</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.603</v>
+        <v>0.171</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2712,39 +2712,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5799300</v>
+        <v>6108200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H49" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.31</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.119</v>
+        <v>0.766</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.106</v>
+        <v>0.751</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2757,39 +2757,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.785</v>
+        <v>0.6</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5695800</v>
+        <v>6007500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H50" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.766</v>
+        <v>0.608</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.751</v>
+        <v>0.603</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2811,19 +2811,19 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.0258</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5522200</v>
+        <v>5918600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="H51" t="n">
-        <v>60.75</v>
+        <v>59.89</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0.74</v>
@@ -2856,19 +2856,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.33</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5512000</v>
+        <v>5575900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="H52" t="n">
-        <v>95.37</v>
+        <v>95.13</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.262</v>
+        <v>0.261</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0.218</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5082800</v>
+        <v>5382800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="H53" t="n">
         <v>68.41</v>
@@ -2937,28 +2937,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.805</v>
+        <v>0.54</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>0.0063</v>
+        <v>0.0286</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5026400</v>
+        <v>5178200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.49</v>
+        <v>0.35</v>
       </c>
       <c r="H54" t="n">
-        <v>49.91</v>
+        <v>68.8</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.804</v>
+        <v>0.466</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.806</v>
+        <v>0.397</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2982,39 +2982,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0.05</v>
+        <v>1.04</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4983800</v>
+        <v>5158700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.1</v>
+        <v>0.64</v>
       </c>
       <c r="H55" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.8</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.103</v>
+        <v>0.875</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.096</v>
+        <v>0.752</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3027,28 +3027,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.54</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>0.0286</v>
+        <v>0.0125</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4982500</v>
+        <v>5118100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.34</v>
+        <v>1.52</v>
       </c>
       <c r="H56" t="n">
-        <v>68.8</v>
+        <v>51.24</v>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.466</v>
+        <v>0.804</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.397</v>
+        <v>0.806</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3072,39 +3072,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>-0.028</v>
+        <v>0.1</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4372300</v>
+        <v>5028300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.54</v>
+        <v>1.11</v>
       </c>
       <c r="H57" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.875</v>
+        <v>0.102</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.752</v>
+        <v>0.096</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3117,28 +3117,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>4.15</v>
+        <v>1.11</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.0641</v>
+        <v>0.0183</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4104700</v>
+        <v>4773100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.93</v>
+        <v>0.39</v>
       </c>
       <c r="H58" t="n">
-        <v>79.69</v>
+        <v>80.11</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>3.488</v>
+        <v>0.997</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>3.204</v>
+        <v>0.837</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3162,28 +3162,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.225</v>
+        <v>4.18</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4103400</v>
+        <v>4613200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.67</v>
+        <v>1.04</v>
       </c>
       <c r="H59" t="n">
-        <v>57.04</v>
+        <v>80.14</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.214</v>
+        <v>3.491</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.211</v>
+        <v>3.205</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3207,28 +3207,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.0367</v>
+        <v>0.0781</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3990200</v>
+        <v>4397200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.32</v>
+        <v>1.94</v>
       </c>
       <c r="H60" t="n">
-        <v>81.51000000000001</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.998</v>
+        <v>2.117</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.838</v>
+        <v>1.74</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3252,28 +3252,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.365</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3932600</v>
+        <v>4182100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.74</v>
+        <v>0.72</v>
       </c>
       <c r="H61" t="n">
-        <v>89.18000000000001</v>
+        <v>48.77</v>
       </c>
       <c r="I61" s="15" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.113</v>
+        <v>0.367</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.739</v>
+        <v>0.366</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3297,28 +3297,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>-0.0267</v>
+        <v>0.225</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3731900</v>
+        <v>4136200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H62" t="n">
-        <v>48.77</v>
+        <v>57.04</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.367</v>
+        <v>0.214</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.366</v>
+        <v>0.211</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3342,28 +3342,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>-0.0175</v>
+        <v>-0.0086</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3451900</v>
+        <v>3875200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>58.3</v>
+        <v>46.5</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.086</v>
+        <v>1.181</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.023</v>
+        <v>1.135</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3387,28 +3387,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.0086</v>
+        <v>0.31</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3328100</v>
+        <v>3851400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="n">
-        <v>46.5</v>
+        <v>61.25</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.181</v>
+        <v>0.307</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.135</v>
+        <v>0.294</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3432,33 +3432,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3324200</v>
+        <v>3769300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
+      </c>
+      <c r="H65" t="n">
+        <v>56.51</v>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
+      <c r="J65" s="9" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>1.023</v>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
     </row>
@@ -3470,28 +3477,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>2.21</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>-0.0391</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3292700</v>
+        <v>3721000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="n">
-        <v>56.16</v>
+        <v>51.04</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3499,10 +3506,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.519</v>
+        <v>2.221</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.473</v>
+        <v>2.099</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3515,28 +3522,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.0171</v>
+        <v>0.535</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3259500</v>
+        <v>3510100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="H67" t="n">
-        <v>34.09</v>
+        <v>56.16</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3544,10 +3551,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>3.623</v>
+        <v>0.519</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>3.707</v>
+        <v>0.473</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3560,39 +3567,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3146700</v>
+        <v>3503000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H68" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.54</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.774</v>
+        <v>0.274</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.773</v>
+        <v>0.316</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3605,40 +3612,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.26</v>
+        <v>0.295</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.0536</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3077000</v>
+        <v>3493100</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H69" t="n">
-        <v>83.89</v>
-      </c>
-      <c r="I69" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>1.024</v>
-      </c>
-      <c r="K69" s="9" t="n">
-        <v>0.876</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3650,39 +3650,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.765</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3019600</v>
+        <v>3443700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="H70" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.15</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.321</v>
+        <v>0.774</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.339</v>
+        <v>0.773</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3695,39 +3695,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.335</v>
+        <v>2.48</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>0.0469</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3010000</v>
+        <v>3417600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.95</v>
+        <v>0.21</v>
       </c>
       <c r="H71" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.335</v>
+        <v>2.434</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.342</v>
+        <v>2.267</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3740,28 +3740,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.21</v>
+        <v>3.44</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>-0.0391</v>
+        <v>-0.0171</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2993500</v>
+        <v>3362800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H72" t="n">
-        <v>51.04</v>
+        <v>34.09</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3769,10 +3769,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.221</v>
+        <v>3.623</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.099</v>
+        <v>3.707</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3785,40 +3785,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2962100</v>
+        <v>3357200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H73" t="n">
-        <v>59.9</v>
+        <v>0.14</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J73" s="9" t="n">
-        <v>2.434</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>2.267</v>
-      </c>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3830,33 +3823,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0.0536</v>
+        <v>2.58</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>-0.0515</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2943600</v>
+        <v>3279500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
+      </c>
+      <c r="H74" t="n">
+        <v>67.95999999999999</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
+      <c r="J74" s="9" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>2.095</v>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3868,28 +3868,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>-0.0077</v>
+        <v>1.25</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2924600</v>
+        <v>3241000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.24</v>
+        <v>1.26</v>
       </c>
       <c r="H75" t="n">
-        <v>33.75</v>
+        <v>83.5</v>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.332</v>
+        <v>1.023</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.452</v>
+        <v>0.876</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3913,28 +3913,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0154</v>
+        <v>1.3</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2908400</v>
+        <v>3222800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>52.57</v>
+        <v>35.36</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.331</v>
+        <v>1.333</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.31</v>
+        <v>1.452</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3958,39 +3958,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0.1098</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2777300</v>
+        <v>3210400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.55</v>
+        <v>1.7</v>
       </c>
       <c r="H77" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.98</v>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.64</v>
+        <v>2.197</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.658</v>
+        <v>1.932</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4003,28 +4003,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.325</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2777200</v>
+        <v>3205400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.09</v>
+        <v>0.38</v>
       </c>
       <c r="H78" t="n">
-        <v>41.51</v>
+        <v>50.52</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.587</v>
+        <v>0.33</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.65</v>
+        <v>0.31</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4048,28 +4048,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.26</v>
+        <v>1.55</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2762200</v>
+        <v>3117500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>4.76</v>
+        <v>1.22</v>
       </c>
       <c r="H79" t="n">
-        <v>55.34</v>
+        <v>39.12</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.253</v>
+        <v>1.586</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.264</v>
+        <v>1.65</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4093,28 +4093,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.265</v>
+        <v>0.605</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2733700</v>
+        <v>3102100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.87</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="n">
-        <v>53.13</v>
+        <v>36.16</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.262</v>
+        <v>0.64</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.25</v>
+        <v>0.658</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4138,28 +4138,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.315</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2732700</v>
+        <v>3065600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="H81" t="n">
-        <v>61.73</v>
+        <v>44.61</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.166</v>
+        <v>0.321</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.098</v>
+        <v>0.339</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4183,39 +4183,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.88</v>
+        <v>0.9</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0112</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2688800</v>
+        <v>3060800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="H82" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.193</v>
+        <v>0.928</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.931</v>
+        <v>0.969</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4228,28 +4228,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.9</v>
+        <v>0.335</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.0469</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2668600</v>
+        <v>3010000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H83" t="n">
-        <v>35.53</v>
+        <v>48.96</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.928</v>
+        <v>0.335</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.969</v>
+        <v>0.342</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4273,39 +4273,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.49</v>
+        <v>1.21</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>-0.0197</v>
+        <v>-0.0163</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2657800</v>
+        <v>2789900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.85</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>4.599</v>
+        <v>1.165</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>4.54</v>
+        <v>1.098</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4318,39 +4318,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>-0.022</v>
+        <v>0.265</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2627400</v>
+        <v>2786200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="H85" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I85" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.13</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3.438</v>
+        <v>0.262</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.295</v>
+        <v>0.25</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4363,39 +4363,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.8</v>
+        <v>4.44</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.022</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2522300</v>
+        <v>2773500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H86" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.14</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>4.851</v>
+        <v>3.438</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>4.967</v>
+        <v>2.295</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4408,28 +4408,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.965</v>
+        <v>4.49</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0446</v>
+        <v>-0.0197</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2439500</v>
+        <v>2772000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="H87" t="n">
-        <v>36.63</v>
+        <v>47.1</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.053</v>
+        <v>4.599</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.011</v>
+        <v>4.54</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4453,28 +4453,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>-0.0135</v>
+        <v>0.26</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2428200</v>
+        <v>2763800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.77</v>
+        <v>4.77</v>
       </c>
       <c r="H88" t="n">
-        <v>54.48</v>
+        <v>55.34</v>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
@@ -4482,9 +4482,11 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.854</v>
-      </c>
-      <c r="K88" s="9" t="n"/>
+        <v>0.253</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.264</v>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
@@ -4496,28 +4498,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0.0278</v>
+        <v>2.92</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2379200</v>
+        <v>2710900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="H89" t="n">
-        <v>84.40000000000001</v>
+        <v>53.97</v>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
@@ -4525,11 +4527,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K89" s="9" t="n">
-        <v>0.79</v>
-      </c>
+        <v>2.853</v>
+      </c>
+      <c r="K89" s="9" t="n"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4541,39 +4541,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.0233</v>
+        <v>4.8</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2346200</v>
+        <v>2686600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="H90" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.63</v>
+        <v>4.851</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.571</v>
+        <v>4.967</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4586,39 +4586,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0.0351</v>
+        <v>0.97</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0396</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2331300</v>
+        <v>2611400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="H91" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I91" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.19</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.592</v>
+        <v>1.053</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.611</v>
+        <v>1.011</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4631,39 +4631,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>-0.0368</v>
+        <v>1.11</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2296000</v>
+        <v>2462100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H92" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.428</v>
+        <v>0.96</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.096</v>
+        <v>0.79</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         <v>-0.012</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2276100</v>
+        <v>2444900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H93" t="n">
         <v>31.96</v>
@@ -4721,28 +4721,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.51</v>
+        <v>0.66</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.0272</v>
+        <v>0.0233</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2238400</v>
+        <v>2419300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="H94" t="n">
-        <v>54.82</v>
+        <v>59.78</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.478</v>
+        <v>0.63</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.536</v>
+        <v>0.571</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4766,39 +4766,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>0.0148</v>
+        <v>0.0331</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2152400</v>
+        <v>2397900</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="H95" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.53</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.677</v>
+        <v>0.8</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.66</v>
+        <v>0.853</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4811,39 +4811,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0.0492</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2120000</v>
+        <v>2336200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.74</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>65.88</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.45</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.889</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.802</v>
+        <v>0.592</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4856,28 +4856,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0.0351</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2110300</v>
+        <v>2332300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.18</v>
+        <v>0.85</v>
       </c>
       <c r="H97" t="n">
-        <v>39.54</v>
+        <v>47.34</v>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.274</v>
+        <v>0.592</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.316</v>
+        <v>0.611</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4901,39 +4901,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.54</v>
+        <v>1.52</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2017700</v>
+        <v>2298900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.3</v>
+        <v>0.92</v>
       </c>
       <c r="H98" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.61</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.479</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.592</v>
+        <v>1.536</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4946,28 +4946,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0.0492</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1761000</v>
+        <v>2240200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.23</v>
+        <v>0.78</v>
       </c>
       <c r="H99" t="n">
-        <v>61.25</v>
+        <v>65.88</v>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.307</v>
+        <v>0.889</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.294</v>
+        <v>0.802</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4991,28 +4991,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.265</v>
+        <v>0.68</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>0.0392</v>
+        <v>0.0074</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1760100</v>
+        <v>2173800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1.35</v>
+        <v>0.21</v>
       </c>
       <c r="H100" t="n">
-        <v>59.89</v>
+        <v>50.85</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.257</v>
+        <v>0.677</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.259</v>
+        <v>0.66</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5036,28 +5036,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1760000</v>
+        <v>2085000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="H101" t="n">
-        <v>31.5</v>
+        <v>30.98</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.053</v>
+        <v>2.679</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.073</v>
+        <v>2.795</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5081,39 +5081,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0.0265</v>
+        <v>1.75</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1759300</v>
+        <v>2081400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H102" t="n">
-        <v>38.81</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.62</v>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.799</v>
+        <v>1.769</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.853</v>
+        <v>1.807</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5126,28 +5126,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0.012</v>
+        <v>6.24</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1707700</v>
+        <v>2022700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H103" t="n">
-        <v>62.57</v>
+        <v>41.98</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.408</v>
+        <v>6.318</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.409</v>
+        <v>6.506</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5171,39 +5171,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.405</v>
+        <v>4.77</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>-0.0122</v>
+        <v>-0.0021</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1697900</v>
+        <v>1947200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1.09</v>
+        <v>0.23</v>
       </c>
       <c r="H104" t="n">
-        <v>70.53</v>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.72</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.368</v>
+        <v>4.746</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.336</v>
+        <v>4.584</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5216,28 +5216,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.38</v>
+        <v>0.58</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.035</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1668500</v>
+        <v>1944900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.73</v>
+        <v>0.51</v>
       </c>
       <c r="H105" t="n">
-        <v>47.07</v>
+        <v>43.05</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.416</v>
+        <v>0.588</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.315</v>
+        <v>0.587</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5261,40 +5261,33 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0.0325</v>
+        <v>0.29</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1622600</v>
+        <v>1928100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H106" t="n">
-        <v>58.73</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="K106" s="9" t="n">
-        <v>0.579</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5306,39 +5299,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>-0.0021</v>
+        <v>3.53</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0.0352</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1617000</v>
+        <v>1921200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.19</v>
+        <v>0.62</v>
       </c>
       <c r="H107" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.55</v>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>4.746</v>
+        <v>3.271</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>4.584</v>
+        <v>2.859</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5360,19 +5353,19 @@
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0.0077</v>
+        <v>2.61</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1603500</v>
+        <v>1881400</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H108" t="n">
-        <v>56.31</v>
+        <v>54.87</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
@@ -5380,10 +5373,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.588</v>
+        <v>2.586</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.433</v>
+        <v>2.432</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5396,39 +5389,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1599500</v>
+        <v>1880200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H109" t="n">
-        <v>70.44</v>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.099</v>
+        <v>1.055</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.999</v>
+        <v>1.073</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5441,39 +5434,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.73</v>
+        <v>4.02</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0.0069</v>
+        <v>0.0308</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1586800</v>
+        <v>1842900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.99</v>
+        <v>0.52</v>
       </c>
       <c r="H110" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.5</v>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.739</v>
+        <v>3.726</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.753</v>
+        <v>3.374</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5486,28 +5479,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>-0.0102</v>
+        <v>0.355</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1579500</v>
+        <v>1824900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>71.70999999999999</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
@@ -5515,10 +5508,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.442</v>
+        <v>0.334</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.402</v>
+        <v>0.318</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5531,39 +5524,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.01</v>
+        <v>1.28</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.0282</v>
+        <v>0.0159</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1567200</v>
+        <v>1820300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H112" t="n">
-        <v>68.20999999999999</v>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.726</v>
+        <v>1.292</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>3.374</v>
+        <v>1.324</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5576,28 +5569,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0.0492</v>
+        <v>1.98</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1552000</v>
+        <v>1798500</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>1.88</v>
+        <v>0.26</v>
       </c>
       <c r="H113" t="n">
-        <v>71.23</v>
+        <v>49.25</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5605,10 +5598,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.297</v>
+        <v>1.989</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.28</v>
+        <v>1.976</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5621,39 +5614,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>-0.0077</v>
+        <v>1.19</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1538900</v>
+        <v>1777500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H114" t="n">
-        <v>31.82</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.44</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.68</v>
+        <v>1.099</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.796</v>
+        <v>0.999</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5666,28 +5659,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3.54</v>
+        <v>0.63</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>0.0381</v>
+        <v>0.0244</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1521100</v>
+        <v>1762500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H115" t="n">
-        <v>73.88</v>
+        <v>57.47</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5695,10 +5688,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>3.272</v>
+        <v>0.614</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.859</v>
+        <v>0.579</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5711,39 +5704,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1503200</v>
+        <v>1760100</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.97</v>
+        <v>1.35</v>
       </c>
       <c r="H116" t="n">
-        <v>46.56</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.295</v>
+        <v>0.257</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.297</v>
+        <v>0.259</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5756,39 +5749,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>7.47</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.0013</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1492700</v>
+        <v>1755800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I117" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.48</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>6.319</v>
+        <v>7.709</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>6.506</v>
+        <v>7.853</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5801,28 +5794,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1479100</v>
+        <v>1755000</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H118" t="n">
-        <v>49.25</v>
+        <v>62.57</v>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
@@ -5830,10 +5823,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.989</v>
+        <v>0.408</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1.976</v>
+        <v>0.409</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5846,39 +5839,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="E119" s="16" t="n">
-        <v>-0.0116</v>
+        <v>-0.035</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1476600</v>
+        <v>1753100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>1.87</v>
+        <v>0.77</v>
       </c>
       <c r="H119" t="n">
-        <v>56</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.07</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.652</v>
+        <v>1.416</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.727</v>
+        <v>1.315</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5891,39 +5884,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E120" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.41</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1476100</v>
+        <v>1737900</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.48</v>
+        <v>1.12</v>
       </c>
       <c r="H120" t="n">
-        <v>52.97</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.7</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.858</v>
+        <v>0.369</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.855</v>
+        <v>0.336</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5936,28 +5929,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0.002</v>
+        <v>1.7</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1468200</v>
+        <v>1688700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.08</v>
+        <v>2.14</v>
       </c>
       <c r="H121" t="n">
-        <v>44.52</v>
+        <v>54.71</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5965,10 +5958,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>10.17</v>
+        <v>1.651</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>10.333</v>
+        <v>1.727</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5981,33 +5974,40 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>-0.0102</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1453200</v>
+        <v>1658200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
+      </c>
+      <c r="H122" t="n">
+        <v>71.70999999999999</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J122" s="9" t="n"/>
-      <c r="K122" s="9" t="n"/>
+      <c r="J122" s="9" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.402</v>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
     </row>
@@ -6019,28 +6019,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0.0123</v>
+        <v>0.525</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1449800</v>
+        <v>1632500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>34.04</v>
+        <v>57.22</v>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>13.506</v>
+        <v>0.511</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>14.083</v>
+        <v>0.461</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6064,28 +6064,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.41</v>
+        <v>7.9</v>
       </c>
       <c r="E124" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0075</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1429200</v>
+        <v>1624100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H124" t="n">
-        <v>53.93</v>
+        <v>57.81</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.399</v>
+        <v>7.786</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.398</v>
+        <v>7.724</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6109,39 +6109,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>7.47</v>
+        <v>0.32</v>
       </c>
       <c r="E125" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.0492</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1418800</v>
+        <v>1607000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.19</v>
+        <v>1.95</v>
       </c>
       <c r="H125" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>7.709</v>
+        <v>0.297</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>7.853</v>
+        <v>0.28</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6154,28 +6154,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.36</v>
+        <v>10.16</v>
       </c>
       <c r="E126" s="17" t="n">
-        <v>0.0286</v>
+        <v>0.004</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1400400</v>
+        <v>1605700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="H126" t="n">
-        <v>65.7</v>
+        <v>46.29</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.334</v>
+        <v>10.171</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.318</v>
+        <v>10.334</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.945</v>
+        <v>0.73</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0216</v>
+        <v>0.0069</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1348500</v>
+        <v>1586800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="H127" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="I127" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.16</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.907</v>
+        <v>0.739</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.776</v>
+        <v>0.753</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6244,28 +6244,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.61</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1292300</v>
+        <v>1558800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H128" t="n">
-        <v>41.55</v>
+        <v>59.86</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.292</v>
+        <v>0.608</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.324</v>
+        <v>0.587</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6289,28 +6289,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.35</v>
+        <v>2.99</v>
       </c>
       <c r="E129" s="16" t="n">
-        <v>-0.0541</v>
+        <v>-0.0033</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1284300</v>
+        <v>1548700</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H129" t="n">
-        <v>53.62</v>
+        <v>47.64</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.351</v>
+        <v>3.011</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.318</v>
+        <v>3.04</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6334,28 +6334,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.525</v>
+        <v>13.24</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0138</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1259900</v>
+        <v>1542800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H130" t="n">
-        <v>52.8</v>
+        <v>34.97</v>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.518</v>
+        <v>13.508</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.53</v>
+        <v>14.083</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6379,39 +6379,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0.0573</v>
+        <v>0.295</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1258300</v>
+        <v>1503200</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H131" t="n">
-        <v>68.12</v>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.56</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.197</v>
+        <v>0.295</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.016</v>
+        <v>0.297</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6424,28 +6424,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.58</v>
+        <v>0.86</v>
       </c>
       <c r="E132" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0058</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1256800</v>
+        <v>1476100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H132" t="n">
-        <v>43.05</v>
+        <v>52.97</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.588</v>
+        <v>0.858</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.587</v>
+        <v>0.855</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6469,28 +6469,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.0059</v>
+        <v>-0.012</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1255900</v>
+        <v>1455000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="H133" t="n">
-        <v>64.22</v>
+        <v>53.93</v>
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.797</v>
+        <v>0.399</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.714</v>
+        <v>0.398</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6514,39 +6514,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EPICON</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>1.89</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1233800</v>
+        <v>1430000</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1.11</v>
+        <v>0.31</v>
       </c>
       <c r="H134" t="n">
-        <v>55.84</v>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.12</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.199</v>
+        <v>1.964</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.206</v>
+        <v>2.085</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6559,39 +6559,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.89</v>
+        <v>0.735</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.028</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1230700</v>
+        <v>1387600</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>36.12</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.70999999999999</v>
+      </c>
+      <c r="I135" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.964</v>
+        <v>0.667</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>2.085</v>
+        <v>0.61</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6604,39 +6604,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E136" s="16" t="n">
+        <v>-0.0209</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1223600</v>
+        <v>1381600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>2.11</v>
+        <v>0.21</v>
       </c>
       <c r="H136" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.247</v>
+        <v>1.919</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.244</v>
+        <v>1.971</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6649,39 +6649,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>1374300</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="I137" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K137" s="9" t="n">
         <v>0.53</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>-0.009300000000000001</v>
-      </c>
-      <c r="F137" s="11" t="n">
-        <v>1220900</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H137" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I137" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J137" s="9" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>0.461</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6694,28 +6694,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.34</v>
+        <v>0.945</v>
       </c>
       <c r="E138" s="17" t="n">
-        <v>0.0091</v>
+        <v>0.0216</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1211700</v>
+        <v>1368700</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H138" t="n">
-        <v>78.62</v>
+        <v>60.38</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>2.909</v>
+        <v>0.907</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.497</v>
+        <v>0.776</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6739,28 +6739,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0573</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1194100</v>
+        <v>1364100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.19</v>
+        <v>0.98</v>
       </c>
       <c r="H139" t="n">
-        <v>47.91</v>
+        <v>68.12</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.77</v>
+        <v>2.197</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.807</v>
+        <v>2.016</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6784,39 +6784,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0.0141</v>
+        <v>0.35</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1181600</v>
+        <v>1304300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H140" t="n">
-        <v>43.39</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.365</v>
+        <v>0.351</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.395</v>
+        <v>0.318</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6829,28 +6829,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>-0.0033</v>
+        <v>0.845</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1159100</v>
+        <v>1295300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H141" t="n">
-        <v>47.64</v>
+        <v>65.62</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>3.011</v>
+        <v>0.797</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>3.04</v>
+        <v>0.714</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6874,39 +6874,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>-0.0157</v>
+        <v>3.35</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1142600</v>
+        <v>1279500</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H142" t="n">
-        <v>43.19</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.84</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.92</v>
+        <v>2.91</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.971</v>
+        <v>2.497</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6919,39 +6919,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1091800</v>
+        <v>1243800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.37</v>
+        <v>1.12</v>
       </c>
       <c r="H143" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.84</v>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.608</v>
+        <v>0.199</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.587</v>
+        <v>0.206</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6964,28 +6964,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1077600</v>
+        <v>1223600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.16</v>
+        <v>2.11</v>
       </c>
       <c r="H144" t="n">
-        <v>51.98</v>
+        <v>55.11</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.566</v>
+        <v>0.247</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.532</v>
+        <v>0.244</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7009,28 +7009,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.655</v>
+        <v>2.59</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>0.0077</v>
+        <v>0.0117</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1055900</v>
+        <v>1196200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="H145" t="n">
-        <v>72.5</v>
+        <v>53.03</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.633</v>
+        <v>2.567</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.589</v>
+        <v>2.532</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7054,28 +7054,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.4</v>
+        <v>0.36</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0141</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1021300</v>
+        <v>1181600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.32</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H146" t="n">
-        <v>60.62</v>
+        <v>43.39</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.341</v>
+        <v>0.365</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.138</v>
+        <v>0.395</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7099,39 +7099,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.74</v>
+        <v>1.4</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.035</v>
+        <v>0.0294</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1001300</v>
+        <v>1168500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H147" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.62</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.668</v>
+        <v>1.341</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.61</v>
+        <v>1.138</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7144,39 +7144,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>-0.0103</v>
+        <v>2.67</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>939100</v>
+        <v>1164400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H148" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45</v>
+      </c>
+      <c r="I148" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>5.808</v>
+        <v>2.679</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>5.731</v>
+        <v>2.884</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7189,39 +7189,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>5.73</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>901200</v>
+        <v>1073000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H149" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="I149" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.5</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.707</v>
+        <v>5.806</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.714</v>
+        <v>5.731</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7234,39 +7234,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E150" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.655</v>
+      </c>
+      <c r="E150" s="17" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>867300</v>
+        <v>1056900</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="H150" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.5</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
         <v>0.633</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.628</v>
+        <v>0.589</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7279,28 +7279,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0101</v>
+        <v>0.255</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>857200</v>
+        <v>1038800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="H151" t="n">
-        <v>56.57</v>
+        <v>48.64</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>7.784</v>
+        <v>0.252</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>7.723</v>
+        <v>0.272</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.615</v>
+        <v>1.08</v>
       </c>
       <c r="E152" s="16" t="n">
-        <v>-0.0315</v>
+        <v>-0.027</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>826300</v>
+        <v>938400</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="H152" t="n">
-        <v>72.16</v>
+        <v>44.61</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.552</v>
+        <v>1.102</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.489</v>
+        <v>1.12</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7369,39 +7369,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>0.0037</v>
+        <v>0.92</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>817700</v>
+        <v>926100</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I153" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.68</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.884</v>
+        <v>0.954</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7414,28 +7414,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>2.02</v>
+        <v>0.72</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>0.0254</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>809700</v>
+        <v>917300</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="H154" t="n">
-        <v>63.89</v>
+        <v>55.83</v>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.87</v>
+        <v>0.707</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.869</v>
+        <v>0.714</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7459,39 +7459,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.62</v>
+        <v>7.72</v>
       </c>
       <c r="E155" s="17" t="n">
-        <v>0.0318</v>
+        <v>0.0198</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>756400</v>
+        <v>912000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="H155" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.83</v>
+      </c>
+      <c r="I155" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.632</v>
+        <v>7.651</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.694</v>
+        <v>7.801</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7504,28 +7504,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>7.73</v>
+        <v>2.03</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>0.0211</v>
+        <v>0.0305</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>748500</v>
+        <v>878000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H156" t="n">
-        <v>51.05</v>
+        <v>64.48</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>7.652</v>
+        <v>1.871</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>7.801</v>
+        <v>1.869</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7549,28 +7549,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>3.19</v>
+        <v>0.63</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>-0.0031</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>745500</v>
+        <v>867300</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="H157" t="n">
-        <v>34.12</v>
+        <v>47.14</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>3.309</v>
+        <v>0.633</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>3.497</v>
+        <v>0.628</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7594,28 +7594,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>0.0114</v>
+        <v>0.615</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>718100</v>
+        <v>843700</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="H158" t="n">
-        <v>66.67</v>
+        <v>72.16</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.822</v>
+        <v>0.552</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.727</v>
+        <v>0.489</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7639,39 +7639,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>8.66</v>
+        <v>1.29</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.0238</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>702900</v>
+        <v>814800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>2.36</v>
+        <v>0.2</v>
       </c>
       <c r="H159" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="I159" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.59</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>8.339</v>
+        <v>1.236</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>1.133</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7684,39 +7684,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>700000</v>
+        <v>810700</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.72</v>
+        <v>0.22</v>
       </c>
       <c r="H160" t="n">
-        <v>48.01</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.05</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.631</v>
+        <v>0.821</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.637</v>
+        <v>0.727</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7738,19 +7738,19 @@
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E161" s="17" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>686000</v>
+        <v>804600</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H161" t="n">
-        <v>43.8</v>
+        <v>45.62</v>
       </c>
       <c r="I161" s="15" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.066</v>
+        <v>2.067</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>2.11</v>
@@ -7774,39 +7774,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E162" s="16" t="n">
-        <v>-0.018</v>
+        <v>7.9</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>660400</v>
+        <v>797900</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="H162" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I162" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.103</v>
+        <v>7.86</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.12</v>
+        <v>7.791</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7819,39 +7819,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>0.008399999999999999</v>
+        <v>3.2</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>658400</v>
+        <v>797500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H163" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I163" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.569</v>
+        <v>3.31</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.575</v>
+        <v>3.497</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7864,28 +7864,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>2.93</v>
+        <v>1.96</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>0.0245</v>
+        <v>0.0103</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>646600</v>
+        <v>793800</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="H164" t="n">
-        <v>60.11</v>
+        <v>47.39</v>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>2.781</v>
+        <v>1.962</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.673</v>
+        <v>2.026</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7909,28 +7909,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>0.0206</v>
+        <v>7.81</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>637400</v>
+        <v>793300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>50.65</v>
+        <v>34.14</v>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.964</v>
+        <v>7.992</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>2.026</v>
+        <v>8.272</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7954,39 +7954,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E166" s="16" t="n">
-        <v>-0.0026</v>
+        <v>1.61</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>631600</v>
+        <v>785500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.05</v>
+        <v>0.57</v>
       </c>
       <c r="H166" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I166" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>7.992</v>
+        <v>1.631</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>8.272</v>
+        <v>1.694</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7999,28 +7999,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>0.0238</v>
+        <v>6.7</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>625700</v>
+        <v>772400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H167" t="n">
-        <v>58.59</v>
+        <v>42.59</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.236</v>
+        <v>6.785</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.133</v>
+        <v>6.79</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8044,28 +8044,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.75</v>
+        <v>2.93</v>
       </c>
       <c r="E168" s="17" t="n">
-        <v>0.0274</v>
+        <v>0.0245</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>621100</v>
+        <v>762600</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>4.88</v>
+        <v>0.25</v>
       </c>
       <c r="H168" t="n">
-        <v>74.87</v>
+        <v>60.11</v>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.672</v>
+        <v>2.781</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.609</v>
+        <v>2.673</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8089,39 +8089,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E169" s="16" t="n">
-        <v>-0.003</v>
+        <v>5.02</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>615200</v>
+        <v>723500</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H169" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.93</v>
+      </c>
+      <c r="I169" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>6.785</v>
+        <v>4.979</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>6.79</v>
+        <v>5.035</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8134,28 +8134,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0</v>
+        <v>4.61</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>598700</v>
+        <v>706800</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2.03</v>
+        <v>0.14</v>
       </c>
       <c r="H170" t="n">
-        <v>59.87</v>
+        <v>37.27</v>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.578</v>
+        <v>4.739</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.53</v>
+        <v>5.008</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8179,28 +8179,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>597800</v>
+        <v>706500</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>2.05</v>
+        <v>0.31</v>
       </c>
       <c r="H171" t="n">
-        <v>40.26</v>
+        <v>31.42</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.846</v>
+        <v>1.153</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8224,39 +8224,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>8.66</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>596300</v>
+        <v>702900</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.14</v>
+        <v>2.36</v>
       </c>
       <c r="H172" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.01</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>7.86</v>
+        <v>8.339</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>7.791</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8269,39 +8269,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>-0.0022</v>
+        <v>0.63</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>588300</v>
+        <v>700000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="H173" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="I173" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.01</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>4.742</v>
+        <v>0.631</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>5.008</v>
+        <v>0.637</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8314,39 +8314,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>0.0177</v>
+        <v>3.01</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>583500</v>
+        <v>680600</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="H174" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="I174" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.61</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.084</v>
+        <v>3.081</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.061</v>
+        <v>3.156</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8359,28 +8359,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E175" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>6.53</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>581400</v>
+        <v>679200</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H175" t="n">
-        <v>48.14</v>
+        <v>30.16</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.64</v>
+        <v>6.739</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.632</v>
+        <v>6.874</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8404,39 +8404,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>3.01</v>
+        <v>5.57</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>-0.0131</v>
+        <v>-0.0124</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>581400</v>
+        <v>675900</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H176" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.03</v>
+      </c>
+      <c r="I176" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>3.081</v>
+        <v>5.723</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>3.156</v>
+        <v>6.099</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8449,28 +8449,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="E177" s="16" t="n">
-        <v>-0.0142</v>
+        <v>0.595</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>564600</v>
+        <v>670500</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H177" t="n">
-        <v>38.7</v>
+        <v>57.39</v>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>5.722</v>
+        <v>0.569</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>6.099</v>
+        <v>0.574</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8494,28 +8494,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>4.98</v>
+        <v>1.27</v>
       </c>
       <c r="E178" s="17" t="n">
-        <v>0.0061</v>
+        <v>0.0242</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>525300</v>
+        <v>655700</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.1</v>
+        <v>0.44</v>
       </c>
       <c r="H178" t="n">
-        <v>49.76</v>
+        <v>45.78</v>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>4.975</v>
+        <v>1.283</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>5.035</v>
+        <v>1.35</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8539,39 +8539,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>8.83</v>
+        <v>0.635</v>
       </c>
       <c r="E179" s="17" t="n">
-        <v>0.0068</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>505100</v>
+        <v>651400</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H179" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="I179" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.14</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>8.689</v>
+        <v>0.64</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>8.548999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8584,28 +8584,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>EITA</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>-0.0048</v>
+        <v>0.75</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>501400</v>
+        <v>628700</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.4</v>
+        <v>4.93</v>
       </c>
       <c r="H180" t="n">
-        <v>40.28</v>
+        <v>74.87</v>
       </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
@@ -8613,16 +8613,511 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>2.083</v>
+        <v>0.672</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>2.112</v>
+        <v>0.609</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>600300</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="H181" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>7252</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TEOSENG</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>597800</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H182" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>595400</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H183" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="I183" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>8.696</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>8.551</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E184" s="17" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>583500</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H184" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>570000</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H185" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>539000</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H186" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="I186" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>534200</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H187" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>9822</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>526400</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H188" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>4.202</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>4.343</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KLK</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>526300</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H189" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="I189" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>22.414</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>21.853</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>-0.0452</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>514600</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H190" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>5.911</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>512800</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H191" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="I191" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M180"/>
+  <autoFilter ref="A1:M191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-25" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-25'!$A$1:$M$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0263</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>14778000</v>
+        <v>14933000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>66.84999999999999</v>
@@ -625,10 +625,10 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6696600</v>
+        <v>6766700</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>69.83</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3突破信号偏强；但RSI达69.83，接近超买区，可靠性略受抑制。</t>
+          <t>现价0.245高于50日均线0.197，EMA20与SAR均呈多头，T3形态突破。RSI 69.83接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>0.125</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7372200</v>
+        <v>7577700</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>6.42</v>
+        <v>6.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>81.89</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头排列，T3突破信号偏强，但超买或加大回调风险。</t>
+          <t>RSI达81.89，处超买区间；现价0.27高于50日均线0.208约30%，EMA20与SAR多头信号虽确认，但短线过热，可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破。RSI 64.42接近超买区但未破70，信号偏强。</t>
+          <t>现价0.56高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 64.42接近超买区但未破70，信号偏强。</t>
         </is>
       </c>
     </row>
@@ -769,28 +769,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.895</v>
+        <v>0.85</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.017</v>
+        <v>0.1039</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1244100</v>
+        <v>24202700</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.15</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.56</v>
+        <v>72.67</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.794</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.895高于50日均线0.794，EMA20与SAR均呈多头，T3突破有效；但RSI达73.56，已进入超买区，信号可靠性偏中性。</t>
+          <t>现价0.85高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达72.67，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -822,28 +822,28 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.865</v>
+        <v>1.41</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1234</v>
+        <v>0.0217</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>23676300</v>
+        <v>1322500</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2.93</v>
+        <v>0.7</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>73.77</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.707</v>
+        <v>1.353</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.324</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -863,62 +863,45 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.865高于50日均线0.685，EMA20与SAR均呈多头，T3形态突破；但RSI达73.77，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>5271</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>PECCA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.0217</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1322500</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>1.353</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>现价1.41高于50日均线1.324，EMA20与SAR均呈多头，T3形态突破；但RSI达72.4，已进入超买区，信号可靠性偏中性。</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0041</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AIMAX</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>396633500</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -928,31 +911,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.015</v>
+        <v>0.19</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>257407400</v>
-      </c>
-      <c r="G9" s="12" t="n"/>
+        <v>51387400</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22.61</v>
+      </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.502</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
     </row>
@@ -964,39 +956,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.19</v>
+        <v>0.025</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>50531300</v>
+        <v>27142700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.08</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.284</v>
+        <v>0.025</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.502</v>
+        <v>0.024</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1009,39 +1001,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>27142700</v>
+        <v>26559000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.28</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.025</v>
+        <v>0.241</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.024</v>
+        <v>0.25</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1054,28 +1046,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0435</v>
+        <v>4.84</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>26044400</v>
+        <v>24465200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="H12" t="n">
-        <v>32.28</v>
+        <v>62.36</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1083,10 +1075,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.241</v>
+        <v>4.724</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.25</v>
+        <v>4.495</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1099,39 +1091,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.0021</v>
+        <v>0.585</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>24416900</v>
+        <v>24248200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="H13" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.34</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>4.725</v>
+        <v>0.543</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>4.495</v>
+        <v>0.491</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1144,28 +1136,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.585</v>
+        <v>0.245</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>24215700</v>
+        <v>22853800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="H14" t="n">
-        <v>71.34</v>
+        <v>31.96</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -1173,10 +1165,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.543</v>
+        <v>0.279</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.491</v>
+        <v>0.33</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1189,28 +1181,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.04</v>
+        <v>0.78</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>22800200</v>
+        <v>18572700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H15" t="n">
-        <v>30.84</v>
+        <v>63.44</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -1218,10 +1210,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.279</v>
+        <v>0.739</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.33</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1249,7 +1241,7 @@
         <v>-0.0375</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>18156300</v>
+        <v>18295600</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>0.39</v>
@@ -1279,28 +1271,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.78</v>
+        <v>0.155</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>17841500</v>
+        <v>17923700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="n">
-        <v>63.44</v>
+        <v>44.71</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1308,10 +1300,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.739</v>
+        <v>0.156</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1333,19 +1325,19 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-0.0313</v>
+        <v>-0.0469</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>16585700</v>
+        <v>16835600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="H18" t="n">
-        <v>61.04</v>
+        <v>59.16</v>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
@@ -1353,7 +1345,7 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0.275</v>
@@ -1369,28 +1361,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.155</v>
+        <v>0.055</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>16073700</v>
+        <v>15911400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.78</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>44.71</v>
+        <v>56.29</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1398,10 +1390,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.156</v>
+        <v>0.053</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.16</v>
+        <v>0.043</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1414,39 +1406,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>15511400</v>
+        <v>15298100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.76</v>
+        <v>0.96</v>
       </c>
       <c r="H20" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.053</v>
+        <v>2.132</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.043</v>
+        <v>2.059</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1459,39 +1451,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0.0145</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>15258800</v>
+        <v>14961000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.95</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>95.37</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>2.132</v>
+        <v>0.837</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.059</v>
+        <v>0.721</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1504,28 +1496,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>14871200</v>
+        <v>13943300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3.33</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
-        <v>95.37</v>
+        <v>59.8</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -1533,10 +1525,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.837</v>
+        <v>0.303</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.721</v>
+        <v>0.29</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1549,28 +1541,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>-0.0159</v>
+        <v>1.85</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.0335</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13943300</v>
+        <v>13647300</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H23" t="n">
-        <v>59.8</v>
+        <v>64.91</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -1578,10 +1570,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.303</v>
+        <v>1.726</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.29</v>
+        <v>1.51</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1594,39 +1586,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.795</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>13605700</v>
+        <v>13431000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.52</v>
+        <v>1.03</v>
       </c>
       <c r="H24" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.35</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.727</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.511</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1639,39 +1631,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>13431000</v>
+        <v>13236300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="H25" t="n">
-        <v>42.35</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1684,28 +1676,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0.0213</v>
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>13072100</v>
+        <v>12840700</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H26" t="n">
-        <v>56.19</v>
+        <v>71.25</v>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
@@ -1713,10 +1705,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.232</v>
+        <v>0.2</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.233</v>
+        <v>0.183</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1729,28 +1721,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.22</v>
+        <v>0.475</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.0435</v>
+        <v>-0.0104</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>12776000</v>
+        <v>11715100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="H27" t="n">
-        <v>71.25</v>
+        <v>52.83</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1758,10 +1750,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.2</v>
+        <v>0.468</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.183</v>
+        <v>0.47</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1783,19 +1775,19 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.0444</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>11601700</v>
+        <v>11703100</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0.93</v>
       </c>
       <c r="H28" t="n">
-        <v>72.83</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -1819,39 +1811,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>-0.0104</v>
+        <v>0.525</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>11581700</v>
+        <v>11477300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.94</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.468</v>
+        <v>0.644</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.47</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1864,28 +1856,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.0095</v>
+        <v>0.45</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>11428500</v>
+        <v>11146000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.29</v>
+        <v>1.44</v>
       </c>
       <c r="H30" t="n">
-        <v>25.6</v>
+        <v>54.08</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1893,10 +1885,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.644</v>
+        <v>0.444</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.863</v>
+        <v>0.403</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1924,7 +1916,7 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>11049200</v>
+        <v>11140000</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0.62</v>
@@ -1954,39 +1946,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.45</v>
+        <v>2.86</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.1042</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>10633600</v>
+        <v>10525900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="H32" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.73</v>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.444</v>
+        <v>2.607</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.403</v>
+        <v>2.484</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1999,28 +1991,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.1081</v>
+        <v>0.765</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>10445500</v>
+        <v>10500400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="H33" t="n">
-        <v>67.09999999999999</v>
+        <v>45.47</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -2028,10 +2020,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.608</v>
+        <v>0.773</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.485</v>
+        <v>0.774</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2089,39 +2081,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>-0.013</v>
+        <v>0.165</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9936400</v>
+        <v>9230800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
       <c r="H35" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.773</v>
+        <v>0.183</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.774</v>
+        <v>0.224</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2149,7 +2141,7 @@
         <v>0.0361</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>9039400</v>
+        <v>9141100</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0.39</v>
@@ -2179,39 +2171,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8898100</v>
+        <v>8756500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.31</v>
+        <v>1.69</v>
       </c>
       <c r="H37" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.72</v>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.183</v>
+        <v>0.678</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.224</v>
+        <v>0.607</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2224,28 +2216,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.765</v>
+        <v>0.955</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0132</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>8587000</v>
+        <v>8646500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="H38" t="n">
-        <v>70.27</v>
+        <v>79.42</v>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
@@ -2253,10 +2245,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.679</v>
+        <v>0.878</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.607</v>
+        <v>0.85</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2284,10 +2276,10 @@
         <v>-0.0432</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8551500</v>
+        <v>8606700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H39" t="n">
         <v>45.67</v>
@@ -2314,39 +2306,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.19</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>8459500</v>
+        <v>8225100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>2.39</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>79.42</v>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.21</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.878</v>
+        <v>0.197</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.85</v>
+        <v>0.196</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2359,39 +2351,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>5.88</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8069100</v>
+        <v>8191400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.98</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.13</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.197</v>
+        <v>5.673</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.196</v>
+        <v>5.099</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2404,28 +2396,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>5.9</v>
+        <v>0.17</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.0172</v>
+        <v>0.0303</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7939100</v>
+        <v>7918000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.53</v>
+        <v>0.17</v>
       </c>
       <c r="H42" t="n">
-        <v>63.7</v>
+        <v>73.31</v>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
@@ -2433,10 +2425,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.675</v>
+        <v>0.142</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.1</v>
+        <v>0.114</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2449,28 +2441,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.17</v>
+        <v>2.41</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0.0303</v>
+        <v>0.0299</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>7776300</v>
+        <v>7818700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>73.31</v>
+        <v>55.74</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
@@ -2478,10 +2470,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.142</v>
+        <v>2.35</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.114</v>
+        <v>2.232</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2494,28 +2486,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.0299</v>
+        <v>0.155</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>7773600</v>
+        <v>6895100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="H44" t="n">
-        <v>55.74</v>
+        <v>49.56</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2523,10 +2515,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.35</v>
+        <v>0.159</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.232</v>
+        <v>0.148</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2554,7 +2546,7 @@
         <v>-0.0185</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6815700</v>
+        <v>6821400</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0.39</v>
@@ -2577,39 +2569,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.115</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6756800</v>
+        <v>6490200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="H46" t="n">
-        <v>49.56</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.159</v>
+        <v>0.119</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.148</v>
+        <v>0.106</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2622,39 +2614,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>6314300</v>
+        <v>6183500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="H47" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.81</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.119</v>
+        <v>0.197</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.106</v>
+        <v>0.171</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2667,28 +2659,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.235</v>
+        <v>0.785</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.0064</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>6143500</v>
+        <v>6108200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H48" t="n">
-        <v>68.06</v>
+        <v>86.31</v>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
@@ -2696,10 +2688,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.197</v>
+        <v>0.766</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.171</v>
+        <v>0.751</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2712,39 +2704,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.785</v>
+        <v>0.605</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>0.0064</v>
+        <v>0.0168</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>6108200</v>
+        <v>6019500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="H49" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.06</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.766</v>
+        <v>0.608</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.751</v>
+        <v>0.603</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2757,39 +2749,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0323</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>6007500</v>
+        <v>5958600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.61</v>
+        <v>2.26</v>
       </c>
       <c r="H50" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.75</v>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.608</v>
+        <v>0.757</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.603</v>
+        <v>0.74</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2802,28 +2794,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.795</v>
+        <v>0.335</v>
       </c>
       <c r="E51" s="17" t="n">
-        <v>0.0258</v>
+        <v>0.0152</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5918600</v>
+        <v>5590200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>2.24</v>
+        <v>0.62</v>
       </c>
       <c r="H51" t="n">
-        <v>59.89</v>
+        <v>95.37</v>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
@@ -2831,10 +2823,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.756</v>
+        <v>0.262</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.74</v>
+        <v>0.218</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2847,28 +2839,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.33</v>
+        <v>0.295</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5575900</v>
+        <v>5383000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="H52" t="n">
-        <v>95.13</v>
+        <v>68.41</v>
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
@@ -2876,10 +2868,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.261</v>
+        <v>0.273</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.218</v>
+        <v>0.269</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2892,28 +2884,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0.0381</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5382800</v>
+        <v>5178700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="H53" t="n">
-        <v>68.41</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
@@ -2921,10 +2913,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.273</v>
+        <v>0.467</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.269</v>
+        <v>0.397</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2937,28 +2929,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0.0286</v>
+        <v>1.04</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5178200</v>
+        <v>5158700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.35</v>
+        <v>0.64</v>
       </c>
       <c r="H54" t="n">
-        <v>68.8</v>
+        <v>77.8</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2966,10 +2958,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.466</v>
+        <v>0.875</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.397</v>
+        <v>0.752</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2982,28 +2974,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>-0.028</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5158700</v>
+        <v>5118800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.64</v>
+        <v>1.52</v>
       </c>
       <c r="H55" t="n">
-        <v>77.8</v>
+        <v>51.24</v>
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
@@ -3011,10 +3003,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.875</v>
+        <v>0.804</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.752</v>
+        <v>0.806</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3027,39 +3019,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0.0125</v>
+        <v>0.1</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>5118100</v>
+        <v>5028300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="H56" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.804</v>
+        <v>0.102</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.806</v>
+        <v>0.096</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3072,39 +3064,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0.0275</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>5028300</v>
+        <v>4821300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.11</v>
+        <v>0.39</v>
       </c>
       <c r="H57" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.83</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.102</v>
+        <v>0.998</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.096</v>
+        <v>0.837</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3117,28 +3109,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.11</v>
+        <v>4.17</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.0183</v>
+        <v>0.0692</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4773100</v>
+        <v>4635200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.39</v>
+        <v>1.05</v>
       </c>
       <c r="H58" t="n">
-        <v>80.11</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3146,10 +3138,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.997</v>
+        <v>3.49</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.837</v>
+        <v>3.205</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3162,28 +3154,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>4.18</v>
+        <v>2.9</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0718</v>
+        <v>0.0781</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4613200</v>
+        <v>4439800</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="H59" t="n">
-        <v>80.14</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
@@ -3191,10 +3183,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.491</v>
+        <v>2.117</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>3.205</v>
+        <v>1.74</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3207,28 +3199,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.9</v>
+        <v>0.225</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.0781</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4397200</v>
+        <v>4201800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.94</v>
+        <v>0.68</v>
       </c>
       <c r="H60" t="n">
-        <v>89.54000000000001</v>
+        <v>57.04</v>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
@@ -3236,10 +3228,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.117</v>
+        <v>0.214</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.74</v>
+        <v>0.211</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3297,28 +3289,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4136200</v>
+        <v>4084000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="H62" t="n">
-        <v>57.04</v>
+        <v>39.54</v>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
@@ -3326,10 +3318,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.214</v>
+        <v>0.274</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.211</v>
+        <v>0.316</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3351,19 +3343,19 @@
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>-0.0086</v>
+        <v>1.16</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3875200</v>
+        <v>3989300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H63" t="n">
-        <v>46.5</v>
+        <v>47.72</v>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
@@ -3371,7 +3363,7 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.181</v>
+        <v>1.182</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>1.135</v>
@@ -3387,28 +3379,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3851400</v>
+        <v>3936400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="H64" t="n">
-        <v>61.25</v>
+        <v>54.65</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3416,10 +3408,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.307</v>
+        <v>0.337</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.294</v>
+        <v>0.332</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3432,39 +3424,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.11</v>
+        <v>2.21</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>-0.0263</v>
+        <v>-0.0391</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3769300</v>
+        <v>3861400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="H65" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I65" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.04</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.085</v>
+        <v>2.221</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.023</v>
+        <v>2.099</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3477,39 +3469,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>-0.0391</v>
+        <v>0.31</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3721000</v>
+        <v>3851400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H66" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.25</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.221</v>
+        <v>0.307</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.099</v>
+        <v>0.294</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3531,19 +3523,19 @@
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.535</v>
+        <v>0.54</v>
       </c>
       <c r="E67" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0189</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3510100</v>
+        <v>3832200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H67" t="n">
-        <v>56.16</v>
+        <v>57.18</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3551,7 +3543,7 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.519</v>
+        <v>0.52</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0.473</v>
@@ -3567,28 +3559,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3503000</v>
+        <v>3789200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H68" t="n">
-        <v>39.54</v>
+        <v>58.3</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3596,10 +3588,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.274</v>
+        <v>1.086</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.316</v>
+        <v>1.023</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3612,33 +3604,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0.0536</v>
+        <v>3.5</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3493100</v>
+        <v>3662800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.15</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H69" t="n">
+        <v>37.22</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
+      <c r="J69" s="9" t="n">
+        <v>3.628</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>3.708</v>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3650,40 +3649,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.0536</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3443700</v>
+        <v>3495900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H70" t="n">
-        <v>46.15</v>
+        <v>0.15</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J70" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>0.773</v>
-      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3695,39 +3687,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.765</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3417600</v>
+        <v>3469700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I71" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.15</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.434</v>
+        <v>0.774</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.267</v>
+        <v>0.773</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3740,39 +3732,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>-0.0171</v>
+        <v>2.48</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3362800</v>
+        <v>3432000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.74</v>
+        <v>0.21</v>
       </c>
       <c r="H72" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.9</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.623</v>
+        <v>2.434</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>3.707</v>
+        <v>2.267</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3785,33 +3777,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.895</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3357200</v>
+        <v>3413000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="H73" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.969</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3823,40 +3822,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>-0.0515</v>
+        <v>0.48</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3279500</v>
+        <v>3358400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H74" t="n">
-        <v>67.95999999999999</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>2.425</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>2.095</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3868,39 +3860,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.08699999999999999</v>
+        <v>2.61</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0404</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3241000</v>
+        <v>3294500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1.26</v>
+        <v>0.57</v>
       </c>
       <c r="H75" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>71.06</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.023</v>
+        <v>2.427</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.876</v>
+        <v>2.095</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3913,28 +3905,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3222800</v>
+        <v>3272100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>1.27</v>
       </c>
       <c r="H76" t="n">
-        <v>35.36</v>
+        <v>83.5</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3942,10 +3934,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.333</v>
+        <v>1.023</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.452</v>
+        <v>0.876</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3967,19 +3959,19 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>0.1098</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3210400</v>
+        <v>3258900</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H77" t="n">
-        <v>89.98</v>
+        <v>89.69</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3987,10 +3979,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.197</v>
+        <v>2.195</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.932</v>
+        <v>1.931</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4003,28 +3995,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3205400</v>
+        <v>3240300</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H78" t="n">
-        <v>50.52</v>
+        <v>33.75</v>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
@@ -4032,10 +4024,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.33</v>
+        <v>1.332</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.31</v>
+        <v>1.452</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4048,28 +4040,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3117500</v>
+        <v>3233100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.22</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>39.12</v>
+        <v>48.43</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4077,10 +4069,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.586</v>
+        <v>0.33</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.65</v>
+        <v>0.31</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4093,39 +4085,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>3102100</v>
+        <v>3232800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="H80" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.91</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.64</v>
+        <v>0.961</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.658</v>
+        <v>0.79</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4138,39 +4130,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.315</v>
+        <v>0.61</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>0.0161</v>
+        <v>0.0083</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>3065600</v>
+        <v>3212200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="H81" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.16</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.321</v>
+        <v>0.641</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.339</v>
+        <v>0.658</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4183,39 +4175,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.9</v>
+        <v>1.56</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>3060800</v>
+        <v>3179100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="H82" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.51</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.928</v>
+        <v>1.587</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.969</v>
+        <v>1.65</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4228,39 +4220,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.335</v>
+        <v>0.315</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>0.0469</v>
+        <v>0.0161</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>3010000</v>
+        <v>3117000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.95</v>
+        <v>0.47</v>
       </c>
       <c r="H83" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.335</v>
+        <v>0.321</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4273,39 +4265,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>-0.0163</v>
+        <v>0.335</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2789900</v>
+        <v>3010000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.3</v>
+        <v>0.95</v>
       </c>
       <c r="H84" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="I84" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.96</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.165</v>
+        <v>0.335</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.098</v>
+        <v>0.342</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4318,39 +4310,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
+        <v>4.41</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2786200</v>
+        <v>2945000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="H85" t="n">
-        <v>53.13</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.262</v>
+        <v>3.436</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.25</v>
+        <v>2.294</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4363,39 +4355,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>4.44</v>
+        <v>1.64</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>-0.022</v>
+        <v>-0.018</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2773500</v>
+        <v>2878000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="H86" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.07</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>3.438</v>
+        <v>1.741</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.295</v>
+        <v>1.855</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4408,39 +4400,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>4.49</v>
+        <v>1.22</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0197</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2772000</v>
+        <v>2849700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H87" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>4.599</v>
+        <v>1.166</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>4.54</v>
+        <v>1.098</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4453,39 +4445,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TUNEPRO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2763800</v>
+        <v>2836700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>4.77</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.8</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.253</v>
+        <v>4.851</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.264</v>
+        <v>4.967</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4498,38 +4490,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.92</v>
+        <v>4.48</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.0218</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2710900</v>
+        <v>2797700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="H89" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.81</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.853</v>
-      </c>
-      <c r="K89" s="9" t="n"/>
+        <v>4.598</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>4.539</v>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
     </row>
@@ -4541,28 +4535,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E90" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.265</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2686600</v>
+        <v>2786200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.13</v>
+        <v>0.88</v>
       </c>
       <c r="H90" t="n">
-        <v>40.8</v>
+        <v>53.13</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4570,10 +4564,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>4.851</v>
+        <v>0.262</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>4.967</v>
+        <v>0.25</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4586,39 +4580,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>TUNEPRO</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0396</v>
+        <v>0.26</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2611400</v>
+        <v>2763800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1.07</v>
+        <v>4.77</v>
       </c>
       <c r="H91" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.053</v>
+        <v>0.253</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.011</v>
+        <v>0.264</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4631,28 +4625,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0.0278</v>
+        <v>2.92</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2462100</v>
+        <v>2754600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.53</v>
+        <v>0.87</v>
       </c>
       <c r="H92" t="n">
-        <v>84.40000000000001</v>
+        <v>53.97</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4660,11 +4654,9 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K92" s="9" t="n">
-        <v>0.79</v>
-      </c>
+        <v>2.853</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4676,28 +4668,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.65</v>
+        <v>0.97</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0396</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2444900</v>
+        <v>2629900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="H93" t="n">
-        <v>31.96</v>
+        <v>37.19</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4705,10 +4697,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.742</v>
+        <v>1.053</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.856</v>
+        <v>1.011</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4721,28 +4713,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.66</v>
+        <v>1.52</v>
       </c>
       <c r="E94" s="17" t="n">
-        <v>0.0233</v>
+        <v>0.034</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2419300</v>
+        <v>2470800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.25</v>
+        <v>0.99</v>
       </c>
       <c r="H94" t="n">
-        <v>59.78</v>
+        <v>56.61</v>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
@@ -4750,10 +4742,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.63</v>
+        <v>1.479</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.571</v>
+        <v>1.536</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4766,39 +4758,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>0.0331</v>
+        <v>0.0233</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2397900</v>
+        <v>2464300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="H95" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.78</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.853</v>
+        <v>0.571</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4811,28 +4803,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.585</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2336200</v>
+        <v>2432900</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="n">
-        <v>36.45</v>
+        <v>46.87</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4840,10 +4832,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.589</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.592</v>
+        <v>0.587</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4856,39 +4848,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="E97" s="17" t="n">
-        <v>0.0351</v>
+        <v>0.0199</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2332300</v>
+        <v>2418100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H97" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.99</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.592</v>
+        <v>0.799</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.611</v>
+        <v>0.852</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4901,39 +4893,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0.034</v>
+        <v>0.535</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2298900</v>
+        <v>2339100</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="H98" t="n">
-        <v>56.61</v>
-      </c>
-      <c r="I98" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.57</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.479</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.536</v>
+        <v>0.592</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4946,28 +4938,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>0.0492</v>
+        <v>0.0351</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2240200</v>
+        <v>2332900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="H99" t="n">
-        <v>65.88</v>
+        <v>47.34</v>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
@@ -4975,10 +4967,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.889</v>
+        <v>0.592</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.802</v>
+        <v>0.611</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -5000,19 +4992,19 @@
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.68</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>0.0074</v>
+        <v>0.0148</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2173800</v>
+        <v>2287100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H100" t="n">
-        <v>50.85</v>
+        <v>51.73</v>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
@@ -5036,39 +5028,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.0115</v>
+        <v>0.96</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0.0492</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2085000</v>
+        <v>2251100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="H101" t="n">
-        <v>30.98</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.88</v>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.679</v>
+        <v>0.889</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.795</v>
+        <v>0.802</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5081,28 +5073,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2081400</v>
+        <v>2124000</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.33</v>
+        <v>0.61</v>
       </c>
       <c r="H102" t="n">
-        <v>46.62</v>
+        <v>71.41</v>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
@@ -5110,10 +5102,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.769</v>
+        <v>1.1</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.807</v>
+        <v>0.999</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5126,28 +5118,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0016</v>
+        <v>1.75</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2022700</v>
+        <v>2117800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H103" t="n">
-        <v>41.98</v>
+        <v>46.62</v>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
@@ -5155,10 +5147,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>6.318</v>
+        <v>1.769</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>6.506</v>
+        <v>1.807</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5171,28 +5163,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.77</v>
+        <v>2.57</v>
       </c>
       <c r="E104" s="16" t="n">
-        <v>-0.0021</v>
+        <v>-0.0115</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1947200</v>
+        <v>2103000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="H104" t="n">
-        <v>55.72</v>
+        <v>30.98</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5200,10 +5192,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>4.746</v>
+        <v>2.679</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>4.584</v>
+        <v>2.795</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5216,39 +5208,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.58</v>
+        <v>6.24</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0016</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1944900</v>
+        <v>2079600</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.51</v>
+        <v>0.12</v>
       </c>
       <c r="H105" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.588</v>
+        <v>6.318</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.587</v>
+        <v>6.506</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5261,33 +5253,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.29</v>
+        <v>4.77</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>-0.0169</v>
+        <v>-0.0021</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1928100</v>
+        <v>2044000</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="H106" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>4.746</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>4.584</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5299,28 +5298,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>3.53</v>
+        <v>2.62</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>0.0352</v>
+        <v>0.0038</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1921200</v>
+        <v>1957400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="H107" t="n">
-        <v>73.55</v>
+        <v>55.6</v>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
@@ -5328,10 +5327,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>3.271</v>
+        <v>2.587</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.859</v>
+        <v>2.433</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5344,40 +5343,33 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1881400</v>
+        <v>1951500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H108" t="n">
-        <v>54.87</v>
+        <v>0.1</v>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J108" s="9" t="n">
-        <v>2.586</v>
-      </c>
-      <c r="K108" s="9" t="n">
-        <v>2.432</v>
-      </c>
+      <c r="J108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
     </row>
@@ -5389,39 +5381,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="E109" s="17" t="n">
-        <v>0.02</v>
+        <v>0.0411</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1880200</v>
+        <v>1921700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.38</v>
+        <v>0.62</v>
       </c>
       <c r="H109" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.2</v>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.055</v>
+        <v>3.273</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.073</v>
+        <v>2.859</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5434,39 +5426,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>4.02</v>
+        <v>1.02</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0.0308</v>
+        <v>0.02</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1842900</v>
+        <v>1884500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="I110" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.726</v>
+        <v>1.055</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>3.374</v>
+        <v>1.073</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5479,39 +5471,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.355</v>
+        <v>0.635</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>0.0143</v>
+        <v>0.0325</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1824900</v>
+        <v>1866700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="H111" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.73</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.334</v>
+        <v>0.614</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.318</v>
+        <v>0.579</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5524,39 +5516,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.28</v>
+        <v>0.355</v>
       </c>
       <c r="E112" s="17" t="n">
-        <v>0.0159</v>
+        <v>0.0143</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1820300</v>
+        <v>1862700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H112" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.01000000000001</v>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.292</v>
+        <v>0.334</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.324</v>
+        <v>0.318</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5569,28 +5561,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0</v>
+        <v>4.01</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0.0282</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1798500</v>
+        <v>1846200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H113" t="n">
-        <v>49.25</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
@@ -5598,10 +5590,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.989</v>
+        <v>3.726</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.976</v>
+        <v>3.374</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5614,39 +5606,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="E114" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0159</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1777500</v>
+        <v>1833200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="H114" t="n">
-        <v>70.44</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.099</v>
+        <v>1.292</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.999</v>
+        <v>1.324</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5659,39 +5651,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0.0244</v>
+        <v>1.98</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1762500</v>
+        <v>1814000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.25</v>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.614</v>
+        <v>1.989</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.579</v>
+        <v>1.976</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5704,39 +5696,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HIAPTEK</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0.0392</v>
+        <v>7.46</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1760100</v>
+        <v>1777600</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1.35</v>
+        <v>0.24</v>
       </c>
       <c r="H116" t="n">
-        <v>59.89</v>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.95</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.257</v>
+        <v>7.708</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.259</v>
+        <v>7.853</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5749,39 +5741,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>7.47</v>
+        <v>10.16</v>
       </c>
       <c r="E117" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.004</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1755800</v>
+        <v>1776300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H117" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>7.709</v>
+        <v>10.171</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>7.853</v>
+        <v>10.334</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5809,7 +5801,7 @@
         <v>0.012</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1755000</v>
+        <v>1761400</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>0.16</v>
@@ -5839,39 +5831,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>HIAPTEK</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>-0.035</v>
+        <v>0.265</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0.0392</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1753100</v>
+        <v>1760100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.77</v>
+        <v>1.35</v>
       </c>
       <c r="H119" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.89</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.416</v>
+        <v>0.257</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.315</v>
+        <v>0.259</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5884,39 +5876,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>1.37</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.042</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1737900</v>
+        <v>1753400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1.12</v>
+        <v>0.77</v>
       </c>
       <c r="H120" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.69</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.369</v>
+        <v>1.415</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.336</v>
+        <v>1.315</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5929,28 +5921,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E121" s="16" t="n">
-        <v>-0.0173</v>
+        <v>0.41</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1688700</v>
+        <v>1738900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>2.14</v>
+        <v>1.12</v>
       </c>
       <c r="H121" t="n">
-        <v>54.71</v>
+        <v>73.7</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5958,10 +5950,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.651</v>
+        <v>0.369</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.727</v>
+        <v>0.336</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5974,28 +5966,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.485</v>
+        <v>0.53</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.0102</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1658200</v>
+        <v>1710000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="H122" t="n">
-        <v>71.70999999999999</v>
+        <v>58.87</v>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
@@ -6003,10 +5995,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.442</v>
+        <v>0.512</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.402</v>
+        <v>0.461</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6019,28 +6011,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.525</v>
+        <v>1.71</v>
       </c>
       <c r="E123" s="16" t="n">
-        <v>-0.0187</v>
+        <v>-0.0116</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1632500</v>
+        <v>1696200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.41</v>
+        <v>2.15</v>
       </c>
       <c r="H123" t="n">
-        <v>57.22</v>
+        <v>56</v>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
@@ -6048,10 +6040,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.511</v>
+        <v>1.652</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.461</v>
+        <v>1.727</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6064,28 +6056,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.9</v>
+        <v>0.485</v>
       </c>
       <c r="E124" s="16" t="n">
-        <v>-0.0075</v>
+        <v>-0.0102</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1624100</v>
+        <v>1693100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="H124" t="n">
-        <v>57.81</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
@@ -6093,10 +6085,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.786</v>
+        <v>0.442</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>7.724</v>
+        <v>0.402</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6109,28 +6101,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.0492</v>
+        <v>7.89</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1607000</v>
+        <v>1659300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>1.95</v>
+        <v>0.12</v>
       </c>
       <c r="H125" t="n">
-        <v>71.23</v>
+        <v>57.19</v>
       </c>
       <c r="I125" s="15" t="inlineStr">
         <is>
@@ -6138,10 +6130,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.297</v>
+        <v>7.785</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.28</v>
+        <v>7.723</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6154,28 +6146,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.004</v>
+        <v>3</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1605700</v>
+        <v>1608900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="H126" t="n">
-        <v>46.29</v>
+        <v>48.52</v>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
@@ -6183,10 +6175,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>10.171</v>
+        <v>3.012</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>10.334</v>
+        <v>3.04</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6199,39 +6191,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0069</v>
+        <v>0.0492</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1586800</v>
+        <v>1607000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.99</v>
+        <v>1.95</v>
       </c>
       <c r="H127" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.23</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.739</v>
+        <v>0.297</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.753</v>
+        <v>0.28</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6244,28 +6236,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1558800</v>
+        <v>1586800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H128" t="n">
-        <v>59.86</v>
+        <v>44.16</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6265,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.608</v>
+        <v>0.739</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.587</v>
+        <v>0.753</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6289,28 +6281,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>-0.0033</v>
+        <v>13.24</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1548700</v>
+        <v>1582600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>47.64</v>
+        <v>34.97</v>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
@@ -6318,10 +6310,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>3.011</v>
+        <v>13.508</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>3.04</v>
+        <v>14.083</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6334,39 +6326,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0.0138</v>
+        <v>0.61</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1542800</v>
+        <v>1558800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H130" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.86</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>13.508</v>
+        <v>0.608</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>14.083</v>
+        <v>0.587</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6379,39 +6371,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1503200</v>
+        <v>1506100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.97</v>
+        <v>0.26</v>
       </c>
       <c r="H131" t="n">
-        <v>46.56</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.93</v>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.295</v>
+        <v>0.399</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.297</v>
+        <v>0.398</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6424,28 +6416,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.295</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1476100</v>
+        <v>1503200</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H132" t="n">
-        <v>52.97</v>
+        <v>46.56</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6453,10 +6445,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.858</v>
+        <v>0.295</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.855</v>
+        <v>0.297</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6469,39 +6461,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0058</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1455000</v>
+        <v>1476100</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="H133" t="n">
-        <v>53.93</v>
-      </c>
-      <c r="I133" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.399</v>
+        <v>0.858</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.398</v>
+        <v>0.855</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6529,10 +6521,10 @@
         <v>0.0053</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1430000</v>
+        <v>1458600</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H134" t="n">
         <v>36.12</v>
@@ -6559,39 +6551,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>0.028</v>
+        <v>1.87</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>-0.0209</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1387600</v>
+        <v>1437900</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>70.70999999999999</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.06</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.667</v>
+        <v>1.919</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.61</v>
+        <v>1.971</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6604,39 +6596,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E136" s="16" t="n">
-        <v>-0.0209</v>
+        <v>0.735</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0.028</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1381600</v>
+        <v>1387600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H136" t="n">
-        <v>42.06</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.70999999999999</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.919</v>
+        <v>0.667</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.971</v>
+        <v>0.61</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6649,28 +6641,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>2.41</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0.0617</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1374300</v>
+        <v>1377500</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="H137" t="n">
-        <v>50.49</v>
+        <v>68.53</v>
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
@@ -6678,10 +6670,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.517</v>
+        <v>2.198</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.53</v>
+        <v>2.016</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6694,28 +6686,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0.0216</v>
+        <v>0.52</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1368700</v>
+        <v>1374300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.79</v>
+        <v>0.23</v>
       </c>
       <c r="H138" t="n">
-        <v>60.38</v>
+        <v>50.49</v>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
@@ -6723,10 +6715,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.907</v>
+        <v>0.517</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.776</v>
+        <v>0.53</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6739,28 +6731,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0.0573</v>
+        <v>0.845</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1364100</v>
+        <v>1370600</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="H139" t="n">
-        <v>68.12</v>
+        <v>65.62</v>
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
@@ -6768,10 +6760,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>2.197</v>
+        <v>0.797</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>2.016</v>
+        <v>0.714</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6784,28 +6776,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>-0.0541</v>
+        <v>0.945</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1304300</v>
+        <v>1368700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="H140" t="n">
-        <v>53.62</v>
+        <v>60.38</v>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
@@ -6813,10 +6805,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.351</v>
+        <v>0.907</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.318</v>
+        <v>0.776</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6829,28 +6821,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1295300</v>
+        <v>1304300</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="H141" t="n">
-        <v>65.62</v>
+        <v>53.62</v>
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
@@ -6858,10 +6850,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.797</v>
+        <v>0.351</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.714</v>
+        <v>0.318</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6889,7 +6881,7 @@
         <v>0.0121</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1279500</v>
+        <v>1293600</v>
       </c>
       <c r="G142" s="12" t="n">
         <v>0.46</v>
@@ -6919,28 +6911,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EPICON</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1243800</v>
+        <v>1274200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="H143" t="n">
-        <v>55.84</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
@@ -6948,10 +6940,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.199</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.206</v>
+        <v>0.794</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6964,28 +6956,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LAYHONG</t>
+          <t>EPICON</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.25</v>
+        <v>0.205</v>
       </c>
       <c r="E144" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1223600</v>
+        <v>1243800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="H144" t="n">
-        <v>55.11</v>
+        <v>55.84</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6993,10 +6985,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.247</v>
+        <v>0.199</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.244</v>
+        <v>0.206</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7009,28 +7001,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>LAYHONG</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0.0117</v>
+        <v>0.25</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1196200</v>
+        <v>1224600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.18</v>
+        <v>2.11</v>
       </c>
       <c r="H145" t="n">
-        <v>53.03</v>
+        <v>55.11</v>
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
@@ -7038,10 +7030,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>2.567</v>
+        <v>0.247</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>2.532</v>
+        <v>0.244</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7054,28 +7046,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.36</v>
+        <v>1.39</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.0141</v>
+        <v>0.0221</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1181600</v>
+        <v>1200300</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H146" t="n">
-        <v>43.39</v>
+        <v>59.81</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7083,10 +7075,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.365</v>
+        <v>1.34</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.395</v>
+        <v>1.138</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7099,39 +7091,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.4</v>
+        <v>2.68</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0294</v>
+        <v>0.0037</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1168500</v>
+        <v>1196400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="H147" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.05</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.341</v>
+        <v>2.68</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.138</v>
+        <v>2.884</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7144,28 +7136,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>0</v>
+        <v>2.59</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1164400</v>
+        <v>1196200</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H148" t="n">
-        <v>45</v>
+        <v>53.03</v>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
@@ -7173,10 +7165,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>2.679</v>
+        <v>2.567</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.884</v>
+        <v>2.532</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7189,28 +7181,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>-0.0138</v>
+        <v>0.355</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1073000</v>
+        <v>1183000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H149" t="n">
-        <v>48.5</v>
+        <v>39.34</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7218,10 +7210,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>5.806</v>
+        <v>0.365</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>5.731</v>
+        <v>0.395</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7234,39 +7226,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>0.0077</v>
+        <v>5.74</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1056900</v>
+        <v>1076100</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H150" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.75</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.633</v>
+        <v>5.807</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.589</v>
+        <v>5.731</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7279,28 +7271,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>0.0408</v>
+        <v>0.65</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1038800</v>
+        <v>1072700</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H151" t="n">
-        <v>48.64</v>
+        <v>70.55</v>
       </c>
       <c r="I151" s="15" t="inlineStr">
         <is>
@@ -7308,10 +7300,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.252</v>
+        <v>0.633</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.272</v>
+        <v>0.589</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7324,28 +7316,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>-0.027</v>
+        <v>0.26</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0.0612</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>938400</v>
+        <v>1049300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H152" t="n">
-        <v>44.61</v>
+        <v>51.5</v>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
@@ -7353,10 +7345,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.102</v>
+        <v>0.253</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.12</v>
+        <v>0.273</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7369,39 +7361,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0108</v>
+        <v>-0.027</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>926100</v>
+        <v>940000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H153" t="n">
-        <v>42.46</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.954</v>
+        <v>1.12</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7414,39 +7406,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.92</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>917300</v>
+        <v>934000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H154" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="I154" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.46</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.707</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.714</v>
+        <v>0.954</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7459,28 +7451,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>0.0198</v>
+        <v>0.615</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>912000</v>
+        <v>924400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.23</v>
+        <v>0.58</v>
       </c>
       <c r="H155" t="n">
-        <v>50.83</v>
+        <v>72.16</v>
       </c>
       <c r="I155" s="15" t="inlineStr">
         <is>
@@ -7488,10 +7480,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>7.651</v>
+        <v>0.552</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>7.801</v>
+        <v>0.489</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7504,28 +7496,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>2.03</v>
+        <v>0.72</v>
       </c>
       <c r="E156" s="17" t="n">
-        <v>0.0305</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>878000</v>
+        <v>917300</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H156" t="n">
-        <v>64.48</v>
+        <v>55.83</v>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
@@ -7533,10 +7525,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.871</v>
+        <v>0.707</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.869</v>
+        <v>0.714</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7549,39 +7541,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>7.75</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>867300</v>
+        <v>915700</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.66</v>
+        <v>0.23</v>
       </c>
       <c r="H157" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.633</v>
+        <v>7.653</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.628</v>
+        <v>7.802</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7594,28 +7586,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>-0.0315</v>
+        <v>2.03</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0.0305</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>843700</v>
+        <v>893600</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="n">
-        <v>72.16</v>
+        <v>64.48</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7623,10 +7615,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.552</v>
+        <v>1.871</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.489</v>
+        <v>1.869</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7639,28 +7631,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>0.0238</v>
+        <v>0.63</v>
+      </c>
+      <c r="E159" s="16" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>814800</v>
+        <v>867300</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="H159" t="n">
-        <v>58.59</v>
+        <v>47.14</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7668,10 +7660,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.236</v>
+        <v>0.633</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.133</v>
+        <v>0.628</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7684,39 +7676,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>3.2</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>810700</v>
+        <v>849100</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>66.05</v>
-      </c>
-      <c r="I160" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.77</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.821</v>
+        <v>3.31</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.727</v>
+        <v>3.497</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7744,10 +7736,10 @@
         <v>0.0049</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>804600</v>
+        <v>848300</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H161" t="n">
         <v>45.62</v>
@@ -7774,28 +7766,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>797900</v>
+        <v>832400</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H162" t="n">
-        <v>53.72</v>
+        <v>58.59</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7803,10 +7795,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>7.86</v>
+        <v>1.236</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>7.791</v>
+        <v>1.133</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7819,39 +7811,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>7.82</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>797500</v>
+        <v>819300</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H163" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.56</v>
+      </c>
+      <c r="I163" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>3.31</v>
+        <v>7.993</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>3.497</v>
+        <v>8.272</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7864,28 +7856,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.96</v>
+        <v>0.89</v>
       </c>
       <c r="E164" s="17" t="n">
-        <v>0.0103</v>
+        <v>0.0171</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>793800</v>
+        <v>813200</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="H164" t="n">
-        <v>47.39</v>
+        <v>67.27</v>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
@@ -7893,10 +7885,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.962</v>
+        <v>0.822</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.026</v>
+        <v>0.727</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7909,39 +7901,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>-0.0026</v>
+        <v>7.9</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>793300</v>
+        <v>812300</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H165" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I165" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>7.992</v>
+        <v>7.86</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>8.272</v>
+        <v>7.791</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7954,28 +7946,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>APEX</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>0.0255</v>
+        <v>0.635</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>785500</v>
+        <v>803500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.57</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H166" t="n">
-        <v>44.92</v>
+        <v>47.79</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7983,10 +7975,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.631</v>
+        <v>0.639</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.694</v>
+        <v>0.645</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7999,39 +7991,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E167" s="16" t="n">
-        <v>-0.003</v>
+        <v>1.98</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0.0206</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>772400</v>
+        <v>797900</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H167" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.65</v>
+      </c>
+      <c r="I167" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>6.785</v>
+        <v>1.964</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>6.79</v>
+        <v>2.026</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8044,39 +8036,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2.93</v>
+        <v>1.61</v>
       </c>
       <c r="E168" s="17" t="n">
-        <v>0.0245</v>
+        <v>0.0255</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>762600</v>
+        <v>789900</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="H168" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="I168" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.92</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>2.781</v>
+        <v>1.631</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>2.673</v>
+        <v>1.694</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8089,39 +8081,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>0.0141</v>
+        <v>6.7</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>723500</v>
+        <v>785200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H169" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="I169" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.59</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>4.979</v>
+        <v>6.785</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>5.035</v>
+        <v>6.79</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8134,28 +8126,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>-0.0086</v>
+        <v>2.94</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>0.028</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>706800</v>
+        <v>768900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
-        <v>37.27</v>
+        <v>60.52</v>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
@@ -8163,10 +8155,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>4.739</v>
+        <v>2.782</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>5.008</v>
+        <v>2.673</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8179,39 +8171,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E171" s="16" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.595</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>706500</v>
+        <v>761600</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="H171" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.39</v>
+      </c>
+      <c r="I171" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.119</v>
+        <v>0.569</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.153</v>
+        <v>0.574</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8224,28 +8216,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UMSINT</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>8.66</v>
+        <v>5.04</v>
       </c>
       <c r="E172" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.0182</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>702900</v>
+        <v>741200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2.36</v>
+        <v>0.14</v>
       </c>
       <c r="H172" t="n">
-        <v>61.01</v>
+        <v>52.94</v>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
@@ -8253,10 +8245,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>8.339</v>
+        <v>4.981</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>8.127000000000001</v>
+        <v>5.036</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8269,28 +8261,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>6.54</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0046</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>700000</v>
+        <v>738200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.72</v>
+        <v>0.15</v>
       </c>
       <c r="H173" t="n">
-        <v>48.01</v>
+        <v>30.62</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8298,10 +8290,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>0.631</v>
+        <v>6.74</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>0.637</v>
+        <v>6.874</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8314,39 +8306,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>3.01</v>
+        <v>4.64</v>
       </c>
       <c r="E174" s="16" t="n">
-        <v>-0.0131</v>
+        <v>-0.0022</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>680600</v>
+        <v>726300</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.66</v>
+        <v>0.15</v>
       </c>
       <c r="H174" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.73</v>
+      </c>
+      <c r="I174" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>3.081</v>
+        <v>4.742</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>3.156</v>
+        <v>5.008</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8359,28 +8351,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>6.53</v>
+        <v>3.01</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>-0.0061</v>
+        <v>-0.0131</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>679200</v>
+        <v>724600</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="H175" t="n">
-        <v>30.16</v>
+        <v>36.61</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8388,10 +8380,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>6.739</v>
+        <v>3.081</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>6.874</v>
+        <v>3.156</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8404,39 +8396,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E176" s="16" t="n">
-        <v>-0.0124</v>
+        <v>1.07</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>675900</v>
+        <v>722200</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H176" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I176" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>5.723</v>
+        <v>1.12</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>6.099</v>
+        <v>1.153</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8449,28 +8441,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0</v>
+        <v>5.56</v>
+      </c>
+      <c r="E177" s="16" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>670500</v>
+        <v>705700</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="H177" t="n">
-        <v>57.39</v>
+        <v>38.7</v>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
@@ -8478,10 +8470,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.569</v>
+        <v>5.722</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.574</v>
+        <v>6.099</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8494,28 +8486,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>UMSINT</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>1.27</v>
+        <v>8.66</v>
       </c>
       <c r="E178" s="17" t="n">
-        <v>0.0242</v>
+        <v>0.0152</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>655700</v>
+        <v>702900</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.44</v>
+        <v>2.36</v>
       </c>
       <c r="H178" t="n">
-        <v>45.78</v>
+        <v>61.01</v>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
@@ -8523,10 +8515,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>1.283</v>
+        <v>8.339</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>1.35</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8539,28 +8531,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.63</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>651400</v>
+        <v>700000</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H179" t="n">
-        <v>48.14</v>
+        <v>48.01</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -8568,10 +8560,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.64</v>
+        <v>0.631</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.632</v>
+        <v>0.637</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8584,39 +8576,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>EITA</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>0.0274</v>
+        <v>0.63</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>628700</v>
+        <v>675200</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>4.93</v>
+        <v>0.26</v>
       </c>
       <c r="H180" t="n">
-        <v>74.87</v>
-      </c>
-      <c r="I180" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.08</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.672</v>
+        <v>0.639</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.609</v>
+        <v>0.632</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8629,28 +8621,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>600300</v>
+        <v>663600</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>2.03</v>
+        <v>0.45</v>
       </c>
       <c r="H181" t="n">
-        <v>59.87</v>
+        <v>45.78</v>
       </c>
       <c r="I181" s="15" t="inlineStr">
         <is>
@@ -8658,10 +8650,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.578</v>
+        <v>1.283</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8674,39 +8666,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>EITA</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>0.0274</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>597800</v>
+        <v>656200</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>2.05</v>
+        <v>5.15</v>
       </c>
       <c r="H182" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.87</v>
+      </c>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.846</v>
+        <v>0.609</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8734,10 +8726,10 @@
         <v>0.0148</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>595400</v>
+        <v>626600</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H183" t="n">
         <v>56.81</v>
@@ -8764,28 +8756,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0265</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>INFOM</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>0.0177</v>
+        <v>1.6</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>583500</v>
+        <v>600300</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.31</v>
+        <v>2.03</v>
       </c>
       <c r="H184" t="n">
-        <v>61.75</v>
+        <v>59.87</v>
       </c>
       <c r="I184" s="15" t="inlineStr">
         <is>
@@ -8793,10 +8785,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>1.084</v>
+        <v>1.578</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>1.061</v>
+        <v>1.53</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8809,39 +8801,39 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E185" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.805</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>570000</v>
+        <v>597800</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.44</v>
+        <v>2.05</v>
       </c>
       <c r="H185" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="I185" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.26</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.627</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.605</v>
+        <v>0.846</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8854,28 +8846,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>0.0177</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>539000</v>
+        <v>583500</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H186" t="n">
-        <v>42.86</v>
+        <v>61.75</v>
       </c>
       <c r="I186" s="15" t="inlineStr">
         <is>
@@ -8883,10 +8875,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>2.084</v>
+        <v>1.084</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>2.112</v>
+        <v>1.061</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8899,39 +8891,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>1.3</v>
+        <v>0.635</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.0076</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>534200</v>
+        <v>572600</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>1.27</v>
+        <v>0.44</v>
       </c>
       <c r="H187" t="n">
-        <v>37.92</v>
-      </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.81</v>
+      </c>
+      <c r="I187" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>1.32</v>
+        <v>0.627</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>1.345</v>
+        <v>0.605</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8944,39 +8936,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E188" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>526400</v>
+        <v>558900</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H188" t="n">
-        <v>40.54</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.28</v>
+      </c>
+      <c r="I188" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>4.202</v>
+        <v>2.083</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>4.343</v>
+        <v>2.112</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8989,28 +8981,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E189" s="17" t="n">
-        <v>0.0009</v>
+        <v>1.5</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>526300</v>
+        <v>545000</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="H189" t="n">
-        <v>54.75</v>
+        <v>30.43</v>
       </c>
       <c r="I189" s="15" t="inlineStr">
         <is>
@@ -9018,10 +9010,10 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>22.414</v>
+        <v>1.565</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>21.853</v>
+        <v>1.681</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -9034,28 +9026,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>5.71</v>
+        <v>1.3</v>
       </c>
       <c r="E190" s="16" t="n">
-        <v>-0.0452</v>
+        <v>-0.0076</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>514600</v>
+        <v>536300</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.84</v>
+        <v>1.28</v>
       </c>
       <c r="H190" t="n">
-        <v>45.69</v>
+        <v>37.92</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9063,10 +9055,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>5.911</v>
+        <v>1.32</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>5.535</v>
+        <v>1.345</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9079,45 +9071,180 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E191" s="10" t="n">
-        <v>0</v>
+        <v>4.02</v>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>512800</v>
+        <v>529800</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.21</v>
+        <v>0.61</v>
       </c>
       <c r="H191" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="I191" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.2</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>1.565</v>
+        <v>4.201</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>1.681</v>
+        <v>4.343</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KLK</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E192" s="17" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H192" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>22.414</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>21.853</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5126</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E193" s="16" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>516600</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H193" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>502200</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H194" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M191"/>
+  <autoFilter ref="A1:M194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -593,12 +593,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，EMA20与SAR均呈多头，T3形态突破；RSI 64.07偏强但未超买，信号技术面较可靠。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面一致性尚可。</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，EMA20与SAR均呈多头，T3形态突破；但RSI达71.13，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.6略低于50日均线0.611，RSI 50.75处中性区间，无超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达79.67，处超买区；现价0.26高于50日均线0.207约25.6%，EMA20与SAR多头信号偏强，但短线过热。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破偏多；但RSI达79.67，已进入超买区，信号可靠性受高位制约。</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价0.55高于50日均线0.395，EMA20与SAR均呈多头，T3形态突破；RSI 63.26未超买，信号技术面偏可靠。</t>
+          <t>现价0.55高于50日均线0.395，RSI 63.26未超买，配合EMA20与SAR多头信号，技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>🎯 EMA20多头 + SAR多头 + T3形态突破</t>
+          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，EMA20与SAR均呈多头，T3形态突破。RSI 70.17已近超买区，信号偏强但需留意短线过热。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热风险。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面一致性尚可。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏积极，但均线压制下可靠性有限。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破偏多；但RSI达79.67，已进入超买区，信号可靠性受高位制约。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破形态成立；但RSI达79.67，已处超买区，信号可靠性受此制约。</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热风险。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破偏多；但RSI达70.17，已近超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面尚属可靠。</t>
+          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性受高位制约。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏积极，但均线压制下可靠性有限。</t>
+          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3突破形态成立；但RSI达79.67，已处超买区，信号可靠性受此制约。</t>
+          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3形态突破；但RSI达79.67，已处超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破偏多；但RSI达70.17，已近超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热。</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
+++ b/docs/downloads/2026-09-25/bursa-report-2026-09-25.xlsx
@@ -557,28 +557,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.66</v>
+        <v>0.25</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0732</v>
+        <v>0.1111</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10285000</v>
+        <v>8860700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.95</v>
+        <v>14.93</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.617</v>
+        <v>0.207</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.579</v>
+        <v>0.197</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.66高于50日均线0.579，RSI 64.07接近超买区，EMA与SAR同向偏多，T3突破信号技术面偏强。</t>
+          <t>现价0.25高于50日均线0.197，RSI达71.13已入超买区，EMA与SAR、Supertrend均偏多，但量能信号需配合观察。</t>
         </is>
       </c>
     </row>
@@ -610,28 +610,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.25</v>
+        <v>3.03</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0341</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8860700</v>
+        <v>29755500</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14.93</v>
+        <v>2.37</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.13</v>
+        <v>71.33</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.207</v>
+        <v>2.846</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.197</v>
+        <v>2.702</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.25高于50日均线0.197，且站上EMA20与SAR，T3突破偏多；但RSI达71.13，已进入超买区，信号可靠性受高位制约。</t>
+          <t>RSI 71.33已超买，现价高于50日均线约12%，EMA与Supertrend偏多，但超买下信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -663,28 +663,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0526</v>
+        <v>0.0649</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3461500</v>
+        <v>37327900</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1.26</v>
+        <v>4.62</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>50.75</v>
+        <v>70.17</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,180 +692,147 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.593</v>
+        <v>0.703</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.611</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
+          <t>🎯 EMA(5) ≥ EMA(20) + SAR &lt; 当前价格 + Supertrend(3,1.4) &lt; 当前价格 + RSI(14) 上穿 70 + 成交量 &gt; 5000000</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.60低于50日均线0.611，RSI 50.75处中性区间，无超买；价格站上EMA20且SAR转多，T3突破信号偏弱，可靠性一般。</t>
+          <t>RSI 70.17 刚进超买区，现价 0.82 高于 50 日均线 0.684 约 20%，均线多头排列，信号偏强但短线过热。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>0373</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>VERDANT</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>11636100</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>79.67</v>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>现价0.26高于50日均线0.207，且站上EMA20与SAR，T3形态突破；但RSI达79.67，已处超买区，信号可靠性需谨慎看待。</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0041</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AIMAX</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>906454100</v>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0455</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>BUSCAP</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0.05769999999999999</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>3286800</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>63.26</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>现价0.55高于50日均线0.395，RSI 63.26未超买，配合EMA20与SAR多头信号，技术面偏强。</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>94950300</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>5184</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>CYPARK</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>37327900</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>70.17</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>🎯 当前价格 &gt; EMA(20) + 当前价格 &gt; SAR + T3 形态突破</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>现价0.82高于50日均线0.684，且站上EMA20与SAR，T3突破形态成立；但RSI达70.17，已进入超买区，信号可靠性需留意短线过热。</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>67728900</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -875,31 +842,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0321</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>906454100</v>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+        <v>39996200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.681</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -911,39 +887,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>1.87</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.0447</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>94950300</v>
+        <v>34693600</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.16</v>
+        <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.284</v>
+        <v>1.728</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.502</v>
+        <v>1.511</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -956,39 +932,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0435</v>
+        <v>0.025</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>67728900</v>
+        <v>33018800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>3.41</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.85</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.241</v>
+        <v>0.025</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.25</v>
+        <v>0.024</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1001,39 +977,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0321</v>
+        <v>4.88</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>39996200</v>
+        <v>31258300</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>56.84</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.34</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.737</v>
+        <v>4.727</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.681</v>
+        <v>4.496</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1046,28 +1022,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0447</v>
+        <v>0.38</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>34693600</v>
+        <v>29898900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.33</v>
+        <v>0.64</v>
       </c>
       <c r="H12" t="n">
-        <v>66</v>
+        <v>76.97</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1075,10 +1051,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.728</v>
+        <v>0.312</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.511</v>
+        <v>0.177</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1091,28 +1067,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.585</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>33018800</v>
+        <v>29693700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="H13" t="n">
-        <v>51.85</v>
+        <v>71.34</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1120,10 +1096,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.025</v>
+        <v>0.543</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.024</v>
+        <v>0.491</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1136,39 +1112,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>31258300</v>
+        <v>28515700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="H14" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.71</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>4.727</v>
+        <v>0.156</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>4.496</v>
+        <v>0.16</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1181,28 +1157,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.05</v>
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>29898900</v>
+        <v>28206900</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>76.97</v>
+        <v>73.31</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1210,10 +1186,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.312</v>
+        <v>0.142</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.177</v>
+        <v>0.114</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1226,28 +1202,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.0341</v>
+        <v>0.32</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>29755500</v>
+        <v>27395700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="H16" t="n">
-        <v>71.33</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1255,10 +1231,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.846</v>
+        <v>0.281</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.702</v>
+        <v>0.276</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1271,28 +1247,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.585</v>
+        <v>0.15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>-0.0168</v>
+        <v>-0.0625</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>29693700</v>
+        <v>26335500</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.27</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>71.34</v>
+        <v>47.65</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1300,10 +1276,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.543</v>
+        <v>0.159</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.491</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1316,28 +1292,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>28515700</v>
+        <v>26303600</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.38</v>
+        <v>0.96</v>
       </c>
       <c r="H18" t="n">
-        <v>44.71</v>
+        <v>31.96</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1345,10 +1321,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.156</v>
+        <v>0.279</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1361,39 +1337,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.0303</v>
+        <v>0.0682</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>28206900</v>
+        <v>24788800</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.6</v>
+        <v>3.19</v>
       </c>
       <c r="H19" t="n">
-        <v>73.31</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.57</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.142</v>
+        <v>0.446</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.114</v>
+        <v>0.403</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1406,28 +1382,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.08470000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>27395700</v>
+        <v>21362400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.68</v>
+        <v>4.79</v>
       </c>
       <c r="H20" t="n">
-        <v>65.18000000000001</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1435,10 +1411,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.281</v>
+        <v>0.836</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.276</v>
+        <v>0.721</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1451,28 +1427,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.15</v>
+        <v>0.475</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>-0.0625</v>
+        <v>-0.0104</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>26335500</v>
+        <v>21005100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H21" t="n">
-        <v>47.65</v>
+        <v>52.83</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1480,10 +1456,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.159</v>
+        <v>0.468</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.148</v>
+        <v>0.47</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1496,28 +1472,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.02</v>
+        <v>0.38</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>26303600</v>
+        <v>20474600</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.96</v>
+        <v>2.27</v>
       </c>
       <c r="H22" t="n">
-        <v>31.96</v>
+        <v>59.86</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1525,10 +1501,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.279</v>
+        <v>0.372</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.33</v>
+        <v>0.371</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1541,39 +1517,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>AHB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.055</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>24788800</v>
+        <v>20422400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>3.19</v>
+        <v>2.32</v>
       </c>
       <c r="H23" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.29</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.446</v>
+        <v>0.053</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.403</v>
+        <v>0.043</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1586,28 +1562,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>21362400</v>
+        <v>19746400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>4.79</v>
+        <v>1.04</v>
       </c>
       <c r="H24" t="n">
-        <v>95.29000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1615,10 +1591,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.836</v>
+        <v>0.303</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.721</v>
+        <v>0.29</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1631,28 +1607,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>-0.0104</v>
+        <v>2.88</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.112</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>21005100</v>
+        <v>19159400</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.84</v>
+        <v>2.99</v>
       </c>
       <c r="H25" t="n">
-        <v>52.83</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1660,10 +1636,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.468</v>
+        <v>2.609</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.47</v>
+        <v>2.485</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1676,28 +1652,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>20474600</v>
+        <v>18610300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2.27</v>
+        <v>1.04</v>
       </c>
       <c r="H26" t="n">
-        <v>59.86</v>
+        <v>41.83</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1705,10 +1681,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.372</v>
+        <v>0.868</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.371</v>
+        <v>0.871</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1721,28 +1697,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AHB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>20422400</v>
+        <v>18388700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2.32</v>
+        <v>0.91</v>
       </c>
       <c r="H27" t="n">
-        <v>56.29</v>
+        <v>71.25</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1750,10 +1726,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.053</v>
+        <v>0.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.043</v>
+        <v>0.183</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1766,39 +1742,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>-0.0159</v>
+        <v>2.09</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>19746400</v>
+        <v>18385700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="H28" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.303</v>
+        <v>2.131</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.29</v>
+        <v>2.059</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1811,39 +1787,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.88</v>
+        <v>0.53</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0.112</v>
+        <v>0.0095</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>19159400</v>
+        <v>17063100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2.99</v>
+        <v>0.44</v>
       </c>
       <c r="H29" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.92</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.609</v>
+        <v>0.645</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.485</v>
+        <v>0.863</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1856,39 +1832,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>-0.0115</v>
+        <v>0.42</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>18610300</v>
+        <v>16720800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="H30" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.36</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.868</v>
+        <v>0.38</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.871</v>
+        <v>0.318</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1901,28 +1877,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>-0.0435</v>
+        <v>0.235</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>18388700</v>
+        <v>16485900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H31" t="n">
-        <v>71.25</v>
+        <v>53.3</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1930,10 +1906,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.2</v>
+        <v>0.231</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.183</v>
+        <v>0.232</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1946,39 +1922,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.09</v>
+        <v>0.805</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.0097</v>
+        <v>0.0063</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>18385700</v>
+        <v>16426000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.15</v>
+        <v>4.87</v>
       </c>
       <c r="H32" t="n">
-        <v>47</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.131</v>
+        <v>0.804</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.059</v>
+        <v>0.806</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1991,28 +1967,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.53</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0.0095</v>
+        <v>0.0189</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>17063100</v>
+        <v>15116900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="H33" t="n">
-        <v>26.92</v>
+        <v>50.2</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -2020,10 +1996,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.645</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.863</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2036,39 +2012,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.42</v>
+        <v>5.89</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.012</v>
+        <v>0.0155</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>16720800</v>
+        <v>14858100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.42</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.38</v>
+        <v>5.674</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.318</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2081,39 +2057,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0145</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TFP</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>16485900</v>
+        <v>14521600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.88</v>
+        <v>4.81</v>
       </c>
       <c r="H35" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.17</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.231</v>
+        <v>0.065</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.232</v>
+        <v>0.074</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2126,28 +2102,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.805</v>
+        <v>0.775</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.0063</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>16426000</v>
+        <v>14276200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4.87</v>
+        <v>1.18</v>
       </c>
       <c r="H36" t="n">
-        <v>49.91</v>
+        <v>50.16</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2155,10 +2131,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.804</v>
+        <v>0.774</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.806</v>
+        <v>0.774</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2171,28 +2147,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0.0189</v>
+        <v>1.8</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.0576</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>15116900</v>
+        <v>14074700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.16</v>
+        <v>2.11</v>
       </c>
       <c r="H37" t="n">
-        <v>50.2</v>
+        <v>35.55</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2200,10 +2176,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.913</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.969</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2216,28 +2192,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>5.89</v>
+        <v>0.95</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.0155</v>
+        <v>0.027</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>14858100</v>
+        <v>13807300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>3.91</v>
       </c>
       <c r="H38" t="n">
-        <v>63.42</v>
+        <v>78.73</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2245,10 +2221,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>5.674</v>
+        <v>0.878</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>5.1</v>
+        <v>0.85</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2261,39 +2237,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0145</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TFP</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.065</v>
+        <v>0.35</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0.0833</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>14521600</v>
+        <v>13658000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>4.81</v>
+        <v>3.99</v>
       </c>
       <c r="H39" t="n">
-        <v>48.17</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.98</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.065</v>
+        <v>0.338</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.074</v>
+        <v>0.332</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2306,28 +2282,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.75</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0066</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>14276200</v>
+        <v>13261000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="H40" t="n">
-        <v>50.16</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2335,10 +2311,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.774</v>
+        <v>0.677</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.774</v>
+        <v>0.607</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2351,28 +2327,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>-0.0576</v>
+        <v>-0.0504</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>14074700</v>
+        <v>13112900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="n">
-        <v>35.55</v>
+        <v>44.52</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2380,10 +2356,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1.913</v>
+        <v>1.38</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1.969</v>
+        <v>1.287</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2396,28 +2372,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.95</v>
+        <v>2.39</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0214</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>13807300</v>
+        <v>12998100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3.91</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
-        <v>78.73</v>
+        <v>54.48</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2425,10 +2401,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.878</v>
+        <v>2.348</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.85</v>
+        <v>2.232</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2441,39 +2417,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.165</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>13658000</v>
+        <v>12466000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>3.99</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.16</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.338</v>
+        <v>0.183</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.332</v>
+        <v>0.224</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2486,39 +2462,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.0066</v>
+        <v>0.78</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>13261000</v>
+        <v>12439500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2.56</v>
+        <v>3.44</v>
       </c>
       <c r="H44" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.53</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.677</v>
+        <v>0.8</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.607</v>
+        <v>0.853</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2531,39 +2507,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0504</v>
+        <v>0.095</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>13112900</v>
+        <v>12331800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.12</v>
+        <v>2.15</v>
       </c>
       <c r="H45" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.43000000000001</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.38</v>
+        <v>0.078</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.287</v>
+        <v>0.067</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2576,28 +2552,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0.0214</v>
+        <v>1.06</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>12998100</v>
+        <v>12302200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.73</v>
+        <v>1.52</v>
       </c>
       <c r="H46" t="n">
-        <v>54.48</v>
+        <v>82.09</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2605,10 +2581,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.348</v>
+        <v>0.877</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.232</v>
+        <v>0.752</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2621,39 +2597,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>2.47</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>12466000</v>
+        <v>11833400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="H47" t="n">
-        <v>34.16</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.91</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.183</v>
+        <v>2.433</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.224</v>
+        <v>2.266</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2666,39 +2642,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0331</v>
+        <v>0.0833</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>12439500</v>
+        <v>11636100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>3.44</v>
+        <v>10.13</v>
       </c>
       <c r="H48" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.67</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.8</v>
+        <v>0.219</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.853</v>
+        <v>0.207</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2711,39 +2687,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.19</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>12331800</v>
+        <v>11477400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="H49" t="n">
-        <v>79.43000000000001</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.21</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.078</v>
+        <v>0.197</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.067</v>
+        <v>0.196</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2756,39 +2732,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0116</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>FOCUS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.005</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>12302200</v>
+        <v>11329300</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="H50" t="n">
-        <v>82.09</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.48</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.877</v>
+        <v>0.006</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.752</v>
+        <v>0.006</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2801,28 +2777,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0.004099999999999999</v>
+        <v>1.95</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>11833400</v>
+        <v>10434800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.72</v>
+        <v>1.52</v>
       </c>
       <c r="H51" t="n">
-        <v>58.91</v>
+        <v>45.48</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2830,10 +2806,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.433</v>
+        <v>1.986</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.266</v>
+        <v>1.976</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2846,39 +2822,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.019</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>11477400</v>
+        <v>10323000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.39</v>
+        <v>0.7</v>
       </c>
       <c r="H52" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.197</v>
+        <v>0.466</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.196</v>
+        <v>0.397</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2891,28 +2867,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0116</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FOCUS</t>
+          <t>OMESTI</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>-0.125</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>11329300</v>
+        <v>10320700</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="H53" t="n">
-        <v>47.48</v>
+        <v>36.98</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2920,10 +2896,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.006</v>
+        <v>0.078</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.006</v>
+        <v>0.077</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2936,28 +2912,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0152</v>
+        <v>0.66</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>10434800</v>
+        <v>10285000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.52</v>
+        <v>2.95</v>
       </c>
       <c r="H54" t="n">
-        <v>45.48</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2965,10 +2941,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.986</v>
+        <v>0.617</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.976</v>
+        <v>0.579</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2981,39 +2957,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0.019</v>
+        <v>4.76</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>10323000</v>
+        <v>9819800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="H55" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.73</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.466</v>
+        <v>4.745</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.397</v>
+        <v>4.584</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -3026,40 +3002,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OMESTI</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>-0.125</v>
+        <v>-0.0556</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>10320700</v>
+        <v>9738400</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H56" t="n">
-        <v>36.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J56" s="9" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="K56" s="9" t="n">
-        <v>0.077</v>
-      </c>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
     </row>
@@ -3071,39 +3040,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.0042</v>
+        <v>0.605</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9819800</v>
+        <v>9471200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="H57" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.06</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>4.745</v>
+        <v>0.608</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>4.584</v>
+        <v>0.603</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3116,33 +3085,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.255</v>
+        <v>4.8</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>-0.0556</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>9738400</v>
+        <v>9095700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
+      </c>
+      <c r="H58" t="n">
+        <v>40.8</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="J58" s="9" t="n">
+        <v>4.851</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>4.967</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3154,28 +3130,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.605</v>
+        <v>0.78</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0168</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9471200</v>
+        <v>9088500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.97</v>
+        <v>3.44</v>
       </c>
       <c r="H59" t="n">
-        <v>48.06</v>
+        <v>57.08</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3183,10 +3159,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.608</v>
+        <v>0.755</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.603</v>
+        <v>0.74</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3199,28 +3175,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.14</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>9095700</v>
+        <v>9051900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.43</v>
+        <v>2.82</v>
       </c>
       <c r="H60" t="n">
-        <v>40.8</v>
+        <v>38.65</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3228,10 +3204,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>4.851</v>
+        <v>0.147</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>4.967</v>
+        <v>0.153</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3244,28 +3220,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9088500</v>
+        <v>8863700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>3.44</v>
+        <v>0.72</v>
       </c>
       <c r="H61" t="n">
-        <v>57.08</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3273,10 +3249,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.755</v>
+        <v>0.996</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.74</v>
+        <v>0.837</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3289,39 +3265,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>9051900</v>
+        <v>8540000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>2.82</v>
+        <v>4.41</v>
       </c>
       <c r="H62" t="n">
-        <v>38.65</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.23</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.147</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.153</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3334,28 +3310,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.1</v>
+        <v>0.18</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0.0092</v>
+        <v>0.1613</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8863700</v>
+        <v>8506600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.72</v>
+        <v>1.71</v>
       </c>
       <c r="H63" t="n">
-        <v>79.31999999999999</v>
+        <v>63.41</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3363,10 +3339,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.996</v>
+        <v>0.161</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.837</v>
+        <v>0.165</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3379,39 +3355,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BINTAI</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>8540000</v>
+        <v>8451400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>4.41</v>
+        <v>0.61</v>
       </c>
       <c r="H64" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.15</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.473</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3424,39 +3400,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0.1613</v>
+        <v>2.23</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>-0.0304</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8506600</v>
+        <v>8307700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="H65" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.43</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.161</v>
+        <v>2.223</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.165</v>
+        <v>2.1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3469,39 +3445,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.0283</v>
+        <v>0.325</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>8451400</v>
+        <v>8186100</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="H66" t="n">
-        <v>58.15</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>90.43000000000001</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.52</v>
+        <v>0.261</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.473</v>
+        <v>0.218</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3514,39 +3490,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>-0.0304</v>
+        <v>4.06</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.04099999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8307700</v>
+        <v>7951900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.16</v>
+        <v>1.79</v>
       </c>
       <c r="H67" t="n">
-        <v>52.43</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.22</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>2.223</v>
+        <v>3.48</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.1</v>
+        <v>3.203</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3559,28 +3535,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>-0.0152</v>
+        <v>2.66</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>8186100</v>
+        <v>7628300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.91</v>
+        <v>0.38</v>
       </c>
       <c r="H68" t="n">
-        <v>90.43000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3588,10 +3564,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.261</v>
+        <v>2.591</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.218</v>
+        <v>2.433</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3604,28 +3580,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.06</v>
+        <v>0.23</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>7951900</v>
+        <v>7560300</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.79</v>
+        <v>0.51</v>
       </c>
       <c r="H69" t="n">
-        <v>78.22</v>
+        <v>66.81</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3633,10 +3609,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.48</v>
+        <v>0.197</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.203</v>
+        <v>0.171</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3649,28 +3625,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0192</v>
+        <v>1.1</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>7628300</v>
+        <v>7456900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="H70" t="n">
-        <v>58.31</v>
+        <v>54.83</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3678,10 +3654,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.591</v>
+        <v>1.084</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.433</v>
+        <v>1.023</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3694,28 +3670,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.0455</v>
+        <v>1.16</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>7560300</v>
+        <v>7434000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H71" t="n">
-        <v>66.81</v>
+        <v>47.72</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3723,10 +3699,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.197</v>
+        <v>1.182</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.171</v>
+        <v>1.135</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3739,39 +3715,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0351</v>
+        <v>0.9</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>7456900</v>
+        <v>7389600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.65</v>
+        <v>2.44</v>
       </c>
       <c r="H72" t="n">
-        <v>54.83</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.53</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.084</v>
+        <v>0.928</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.023</v>
+        <v>0.969</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3784,28 +3760,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.06320000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>7434000</v>
+        <v>7329400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.07</v>
+        <v>3.24</v>
       </c>
       <c r="H73" t="n">
-        <v>47.72</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3813,10 +3789,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.182</v>
+        <v>2.113</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.135</v>
+        <v>1.739</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3829,39 +3805,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.9</v>
+        <v>0.785</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>0.0112</v>
+        <v>0.0064</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>7389600</v>
+        <v>7277600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>2.44</v>
+        <v>1.28</v>
       </c>
       <c r="H74" t="n">
-        <v>35.53</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.31</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.928</v>
+        <v>0.766</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.969</v>
+        <v>0.751</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3874,39 +3850,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PERMAJU</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.01</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>7329400</v>
+        <v>7209300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>3.24</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>89.18000000000001</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.65</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.113</v>
+        <v>0.007</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.739</v>
+        <v>0.008</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3919,39 +3895,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0064</v>
+        <v>1.63</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>7277600</v>
+        <v>7202300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="H76" t="n">
-        <v>86.31</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.24</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.766</v>
+        <v>1.74</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.751</v>
+        <v>1.855</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3964,28 +3940,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PERMAJU</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0.0187</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>7209300</v>
+        <v>7131600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>78.23999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="H77" t="n">
-        <v>58.65</v>
+        <v>39.08</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3993,10 +3969,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.007</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.008</v>
+        <v>0.592</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -4009,28 +3985,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>-0.024</v>
+        <v>0.115</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>7202300</v>
+        <v>7024200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>30.24</v>
+        <v>48.46</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4038,10 +4014,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.74</v>
+        <v>0.119</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.855</v>
+        <v>0.106</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4054,39 +4030,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0.0187</v>
+        <v>0.29</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>7131600</v>
+        <v>6973800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="H79" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.81</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.273</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.592</v>
+        <v>0.269</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4099,40 +4075,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>2.96</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>7024200</v>
+        <v>6719400</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="H80" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.05</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="K80" s="9" t="n">
-        <v>0.106</v>
-      </c>
+        <v>2.857</v>
+      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4144,28 +4118,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>-0.0169</v>
+        <v>-0.0133</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>6973800</v>
+        <v>6554300</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="n">
-        <v>63.81</v>
+        <v>52.41</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4173,10 +4147,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.273</v>
+        <v>0.367</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.269</v>
+        <v>0.366</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4189,38 +4163,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.0034</v>
+        <v>0.61</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6719400</v>
+        <v>6510000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="H82" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.16</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.857</v>
-      </c>
-      <c r="K82" s="9" t="n"/>
+        <v>0.641</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.658</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4232,39 +4208,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0133</v>
+        <v>-0.0169</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>6554300</v>
+        <v>6474800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.12</v>
+        <v>4.2</v>
       </c>
       <c r="H83" t="n">
-        <v>52.41</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.28</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.367</v>
+        <v>0.295</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.366</v>
+        <v>0.297</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4277,39 +4253,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>6510000</v>
+        <v>6464300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="H84" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.91</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.641</v>
+        <v>0.961</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.658</v>
+        <v>0.79</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4322,28 +4298,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.29</v>
+        <v>0.765</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0169</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6474800</v>
+        <v>6443400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="n">
-        <v>31.28</v>
+        <v>46.15</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4351,10 +4327,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.295</v>
+        <v>0.774</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.297</v>
+        <v>0.773</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4367,39 +4343,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.03700000000000001</v>
+        <v>4.49</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.0197</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>6464300</v>
+        <v>6418400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.39</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="n">
-        <v>84.91</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.1</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.961</v>
+        <v>4.599</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.79</v>
+        <v>4.54</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4412,39 +4388,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PESTEC</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.055</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>6443400</v>
+        <v>6318100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="H87" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.3</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.774</v>
+        <v>0.057</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.773</v>
+        <v>0.06</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4457,39 +4433,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MKLAND</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.0197</v>
+        <v>0.175</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0.09369999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>6418400</v>
+        <v>6313200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.85</v>
+        <v>8.1</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.93000000000001</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.599</v>
+        <v>0.149</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>4.54</v>
+        <v>0.145</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4502,28 +4478,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PESTEC</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0.0682</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>6318100</v>
+        <v>6298900</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1.45</v>
+        <v>3.33</v>
       </c>
       <c r="H89" t="n">
-        <v>39.3</v>
+        <v>88.84</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4531,10 +4507,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.057</v>
+        <v>2.187</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.06</v>
+        <v>1.93</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4547,39 +4523,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MKLAND</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.09369999999999999</v>
+        <v>7.46</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>6313200</v>
+        <v>6268000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>8.1</v>
+        <v>0.86</v>
       </c>
       <c r="H90" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.95</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.149</v>
+        <v>7.708</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.145</v>
+        <v>7.853</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4592,28 +4568,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.82</v>
+        <v>0.22</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>0.0682</v>
+        <v>0.0233</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>6298900</v>
+        <v>6254900</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>3.33</v>
+        <v>1.02</v>
       </c>
       <c r="H91" t="n">
-        <v>88.84</v>
+        <v>54.39</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4621,10 +4597,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.187</v>
+        <v>0.214</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.93</v>
+        <v>0.211</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4637,39 +4613,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>7.46</v>
+        <v>0.26</v>
       </c>
       <c r="E92" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>6268000</v>
+        <v>6180200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="H92" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.54</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>7.708</v>
+        <v>0.274</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>7.853</v>
+        <v>0.316</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4682,39 +4658,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0.0233</v>
+        <v>3.49</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>-0.0029</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>6254900</v>
+        <v>6126900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="H93" t="n">
-        <v>54.39</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.66</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.214</v>
+        <v>3.627</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.211</v>
+        <v>3.708</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4727,39 +4703,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0178</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SEDANIA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>6180200</v>
+        <v>6123100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="H94" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.7</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.274</v>
+        <v>0.102</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.316</v>
+        <v>0.096</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4772,28 +4748,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>JADI</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>-0.0029</v>
+        <v>0.03</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0.2</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>6126900</v>
+        <v>6000000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.35</v>
+        <v>30</v>
       </c>
       <c r="H95" t="n">
-        <v>36.66</v>
+        <v>48.54</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4801,10 +4777,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>3.627</v>
+        <v>0.03</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>3.708</v>
+        <v>0.034</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4817,39 +4793,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0178</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SEDANIA</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0</v>
+        <v>6.24</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>6123100</v>
+        <v>5968700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.35</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.98</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.102</v>
+        <v>6.318</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.096</v>
+        <v>6.506</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4862,39 +4838,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>0452</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JADI</t>
+          <t>GOLDLI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0.2</v>
+        <v>0.095</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>6000000</v>
+        <v>5876700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>30</v>
+        <v>6.11</v>
       </c>
       <c r="H97" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.2</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.03</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.034</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4907,28 +4883,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>-0.0016</v>
+        <v>13.14</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>5968700</v>
+        <v>5767700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
       <c r="H98" t="n">
-        <v>41.98</v>
+        <v>30.03</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4936,10 +4912,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>6.318</v>
+        <v>13.498</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>6.506</v>
+        <v>14.081</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4952,28 +4928,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0452</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GOLDLI</t>
+          <t>CFM</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.095</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E99" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>5876700</v>
+        <v>5704000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>6.11</v>
+        <v>2.85</v>
       </c>
       <c r="H99" t="n">
-        <v>63.2</v>
+        <v>67.5</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4981,10 +4957,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4997,39 +4973,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0.0061</v>
+        <v>2.57</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>5767700</v>
+        <v>5630600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.6</v>
+        <v>1.77</v>
       </c>
       <c r="H100" t="n">
-        <v>30.03</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.98</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>13.498</v>
+        <v>2.679</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>14.081</v>
+        <v>2.795</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5042,28 +5018,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CFM</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>5704000</v>
+        <v>5614200</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="H101" t="n">
-        <v>67.5</v>
+        <v>41.51</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5071,10 +5047,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.075</v>
+        <v>1.587</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5087,39 +5063,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.57</v>
+        <v>4.35</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>-0.0115</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>5630600</v>
+        <v>5580200</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.77</v>
+        <v>0.47</v>
       </c>
       <c r="H102" t="n">
-        <v>30.98</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.81</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.679</v>
+        <v>3.43</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.795</v>
+        <v>2.293</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5132,28 +5108,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.56</v>
+        <v>0.695</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0296</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>5614200</v>
+        <v>5519800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>2.2</v>
+        <v>0.53</v>
       </c>
       <c r="H103" t="n">
-        <v>41.51</v>
+        <v>53.42</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5161,10 +5137,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.587</v>
+        <v>0.678</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.65</v>
+        <v>0.66</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5177,40 +5153,33 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>-0.04190000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>5580200</v>
+        <v>5465000</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H104" t="n">
-        <v>78.81</v>
+        <v>0.23</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J104" s="9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>2.293</v>
-      </c>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
     </row>
@@ -5222,28 +5191,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0.0296</v>
+        <v>1.2</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>5519800</v>
+        <v>5453300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="H105" t="n">
-        <v>53.42</v>
+        <v>58.08</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5251,10 +5220,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.678</v>
+        <v>1.164</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.66</v>
+        <v>1.098</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5267,33 +5236,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>SINARAN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.48</v>
+        <v>0.105</v>
       </c>
       <c r="E106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>5465000</v>
+        <v>5409700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.23</v>
+        <v>2.42</v>
+      </c>
+      <c r="H106" t="n">
+        <v>51.1</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
+      <c r="J106" s="9" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.102</v>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
     </row>
@@ -5305,39 +5281,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>-0.0244</v>
+        <v>0.115</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>5453300</v>
+        <v>5320600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H107" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.81</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.164</v>
+        <v>0.123</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.098</v>
+        <v>0.122</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5350,28 +5326,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SINARAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>5409700</v>
+        <v>5245700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>2.42</v>
+        <v>0.39</v>
       </c>
       <c r="H108" t="n">
-        <v>51.1</v>
+        <v>57.81</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5379,10 +5355,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.104</v>
+        <v>7.786</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.102</v>
+        <v>7.724</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5395,39 +5371,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>5320600</v>
+        <v>5094400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.55</v>
+        <v>2.03</v>
       </c>
       <c r="H109" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.87</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.123</v>
+        <v>1.477</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.122</v>
+        <v>1.536</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5440,28 +5416,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>-0.0075</v>
+        <v>0.42</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0.012</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>5245700</v>
+        <v>5066900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H110" t="n">
-        <v>57.81</v>
+        <v>62.57</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5469,10 +5445,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.786</v>
+        <v>0.408</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.724</v>
+        <v>0.409</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5485,28 +5461,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.5</v>
+        <v>10.22</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>0.0204</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>5094400</v>
+        <v>4990400</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>2.03</v>
+        <v>0.29</v>
       </c>
       <c r="H111" t="n">
-        <v>52.87</v>
+        <v>50.98</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5514,10 +5490,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.477</v>
+        <v>10.177</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.536</v>
+        <v>10.335</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5530,28 +5506,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0.012</v>
+        <v>1.29</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>5066900</v>
+        <v>4912700</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="H112" t="n">
-        <v>62.57</v>
+        <v>33.75</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5559,10 +5535,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.408</v>
+        <v>1.332</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.409</v>
+        <v>1.452</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5575,39 +5551,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0363</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>PMCK</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>10.22</v>
+        <v>0.195</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0263</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>4990400</v>
+        <v>4850800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.29</v>
+        <v>11.17</v>
       </c>
       <c r="H113" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>10.177</v>
+        <v>0.198</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>10.335</v>
+        <v>0.2</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5620,40 +5596,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>-0.0077</v>
+        <v>0.29</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>4912700</v>
+        <v>4691000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H114" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="K114" s="9" t="n">
-        <v>1.452</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
@@ -5665,39 +5634,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0363</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PMCK</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0.0263</v>
+        <v>0.325</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>4850800</v>
+        <v>4688000</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>11.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.52</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.198</v>
+        <v>0.33</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5710,33 +5679,40 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.29</v>
+        <v>0.98</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>0.0357</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>4691000</v>
+        <v>4473500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J116" s="9" t="n"/>
-      <c r="K116" s="9" t="n"/>
+        <v>1.56</v>
+      </c>
+      <c r="H116" t="n">
+        <v>67.97</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.802</v>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
     </row>
@@ -5748,39 +5724,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>4688000</v>
+        <v>4472100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="H117" t="n">
-        <v>50.52</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.46</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.33</v>
+        <v>1.055</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.31</v>
+        <v>1.073</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5793,28 +5769,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>0.07099999999999999</v>
+        <v>2.67</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>4473500</v>
+        <v>4405600</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>1.56</v>
+        <v>0.46</v>
       </c>
       <c r="H118" t="n">
-        <v>67.97</v>
+        <v>45</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5822,10 +5798,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.891</v>
+        <v>2.679</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.802</v>
+        <v>2.884</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5838,28 +5814,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>0.02</v>
+        <v>2.7</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>4472100</v>
+        <v>4361300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="H119" t="n">
-        <v>38.46</v>
+        <v>82.33</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5867,10 +5843,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.055</v>
+        <v>2.436</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.073</v>
+        <v>2.097</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5883,28 +5859,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>4405600</v>
+        <v>4272100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
       <c r="H120" t="n">
-        <v>45</v>
+        <v>71.41</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
@@ -5912,10 +5888,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>2.679</v>
+        <v>1.1</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>2.884</v>
+        <v>0.999</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5928,39 +5904,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>-0.0074</v>
+        <v>0.845</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>4361300</v>
+        <v>4260100</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.76</v>
+        <v>1.51</v>
       </c>
       <c r="H121" t="n">
-        <v>82.33</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.436</v>
+        <v>0.797</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.097</v>
+        <v>0.714</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5973,39 +5949,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>0.0169</v>
+        <v>0.0159</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>4272100</v>
+        <v>4150400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
       <c r="H122" t="n">
-        <v>71.41</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.1</v>
+        <v>1.292</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.999</v>
+        <v>1.324</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6018,28 +5994,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4260100</v>
+        <v>4123800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>1.51</v>
+        <v>0.62</v>
       </c>
       <c r="H123" t="n">
-        <v>65.62</v>
+        <v>47.42</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6047,10 +6023,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.797</v>
+        <v>0.321</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.714</v>
+        <v>0.339</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6063,39 +6039,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.28</v>
+        <v>0.425</v>
       </c>
       <c r="E124" s="17" t="n">
-        <v>0.0159</v>
+        <v>0.0241</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>4150400</v>
+        <v>4118500</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="H124" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.85</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.292</v>
+        <v>0.4</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.324</v>
+        <v>0.399</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6108,40 +6084,33 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.285</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>4123800</v>
+        <v>4029500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H125" t="n">
-        <v>47.42</v>
+        <v>0.21</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J125" s="9" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="K125" s="9" t="n">
-        <v>0.339</v>
-      </c>
+      <c r="J125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
     </row>
@@ -6153,39 +6122,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.0241</v>
+        <v>0.98</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>-0.0297</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>4118500</v>
+        <v>3988400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.7</v>
+        <v>1.64</v>
       </c>
       <c r="H126" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.36</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.4</v>
+        <v>1.054</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.399</v>
+        <v>1.011</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6198,33 +6167,40 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>-0.0339</v>
+        <v>0.29</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>4029500</v>
+        <v>3985400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.21</v>
+        <v>0.51</v>
+      </c>
+      <c r="H127" t="n">
+        <v>39.09</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J127" s="9" t="n"/>
-      <c r="K127" s="9" t="n"/>
+      <c r="J127" s="9" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>0.312</v>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
     </row>
@@ -6236,39 +6212,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>-0.0297</v>
+        <v>1.39</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>3988400</v>
+        <v>3910600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="H128" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.28</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.054</v>
+        <v>1.351</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.011</v>
+        <v>1.323</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6281,39 +6257,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>3985400</v>
+        <v>3908400</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.51</v>
+        <v>1.24</v>
       </c>
       <c r="H129" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.299</v>
+        <v>0.262</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.312</v>
+        <v>0.25</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6326,39 +6302,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0.0072</v>
+        <v>0.715</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3910600</v>
+        <v>3903800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="H130" t="n">
-        <v>68.28</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.09</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.351</v>
+        <v>0.737</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.323</v>
+        <v>0.753</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6371,39 +6347,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>-0.0189</v>
+        <v>3.63</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0.0645</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3908400</v>
+        <v>3894700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="H131" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.5</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.262</v>
+        <v>3.281</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.25</v>
+        <v>2.861</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6416,39 +6392,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>-0.0138</v>
+        <v>1.24</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0.07829999999999999</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>3903800</v>
+        <v>3892000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="H132" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.737</v>
+        <v>1.023</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.753</v>
+        <v>0.876</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6461,28 +6437,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.0645</v>
+        <v>0.31</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>3894700</v>
+        <v>3852400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1.27</v>
+        <v>0.51</v>
       </c>
       <c r="H133" t="n">
-        <v>76.5</v>
+        <v>61.25</v>
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
@@ -6490,10 +6466,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.281</v>
+        <v>0.307</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.861</v>
+        <v>0.294</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6506,28 +6482,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.24</v>
+        <v>0.66</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>3892000</v>
+        <v>3817500</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1.51</v>
+        <v>0.4</v>
       </c>
       <c r="H134" t="n">
-        <v>83.09999999999999</v>
+        <v>59.78</v>
       </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
@@ -6535,10 +6511,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.023</v>
+        <v>0.63</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.876</v>
+        <v>0.571</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6551,28 +6527,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>1.78</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>3852400</v>
+        <v>3806300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H135" t="n">
-        <v>61.25</v>
+        <v>50.3</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6580,10 +6556,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.307</v>
+        <v>1.772</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.294</v>
+        <v>1.808</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6596,39 +6572,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E136" s="17" t="n">
-        <v>0.0233</v>
+        <v>6.69</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>3817500</v>
+        <v>3792700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.4</v>
+        <v>0.89</v>
       </c>
       <c r="H136" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.9</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.63</v>
+        <v>6.785</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.571</v>
+        <v>6.79</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6641,28 +6617,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0111</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.78</v>
+        <v>0.16</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>0.0171</v>
+        <v>0.0667</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3806300</v>
+        <v>3783100</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.61</v>
+        <v>1.56</v>
       </c>
       <c r="H137" t="n">
-        <v>50.3</v>
+        <v>63.84</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
@@ -6670,10 +6646,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.772</v>
+        <v>0.146</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.808</v>
+        <v>0.138</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6686,39 +6662,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>-0.004500000000000001</v>
+        <v>2.62</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>3792700</v>
+        <v>3729800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H138" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>6.785</v>
+        <v>2.57</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>6.79</v>
+        <v>2.532</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6731,28 +6707,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0111</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0.0667</v>
+        <v>0.49</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>3783100</v>
+        <v>3700200</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="H139" t="n">
-        <v>63.84</v>
+        <v>74.59</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6760,10 +6736,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.146</v>
+        <v>0.443</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.138</v>
+        <v>0.402</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6776,39 +6752,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0.0234</v>
+        <v>0.58</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>3729800</v>
+        <v>3683600</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H140" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.05</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.57</v>
+        <v>0.588</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.532</v>
+        <v>0.587</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6821,39 +6797,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>0.105</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>3700200</v>
+        <v>3642200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>1.15</v>
+        <v>0.14</v>
       </c>
       <c r="H141" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.42</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.443</v>
+        <v>0.137</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.402</v>
+        <v>0.164</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6866,39 +6842,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CJCEN</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.185</v>
+      </c>
+      <c r="E142" s="17" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>3683600</v>
+        <v>3616700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.96</v>
+        <v>13.77</v>
       </c>
       <c r="H142" t="n">
-        <v>43.05</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.75</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.588</v>
+        <v>0.169</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.587</v>
+        <v>0.162</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6911,39 +6887,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>-0.0455</v>
+        <v>5.05</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>3642200</v>
+        <v>3569500</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="H143" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.43</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.137</v>
+        <v>4.982</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.164</v>
+        <v>5.036</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6956,28 +6932,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CJCEN</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.185</v>
+        <v>2.17</v>
       </c>
       <c r="E144" s="17" t="n">
-        <v>0.0571</v>
+        <v>0.1015</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>3616700</v>
+        <v>3530500</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>13.77</v>
+        <v>1.8</v>
       </c>
       <c r="H144" t="n">
-        <v>74.75</v>
+        <v>71.16</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6985,10 +6961,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.169</v>
+        <v>1.884</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.162</v>
+        <v>1.872</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7001,28 +6977,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>5.05</v>
+        <v>3.01</v>
       </c>
       <c r="E145" s="17" t="n">
-        <v>0.0202</v>
+        <v>0.0033</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>3569500</v>
+        <v>3468000</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.65</v>
+        <v>1.07</v>
       </c>
       <c r="H145" t="n">
-        <v>53.43</v>
+        <v>49.45</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7030,10 +7006,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>4.982</v>
+        <v>3.013</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>5.036</v>
+        <v>3.041</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7046,28 +7022,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>2.17</v>
+        <v>0.6</v>
       </c>
       <c r="E146" s="17" t="n">
-        <v>0.1015</v>
+        <v>0.0526</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>3530500</v>
+        <v>3461500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>1.8</v>
+        <v>1.26</v>
       </c>
       <c r="H146" t="n">
-        <v>71.16</v>
+        <v>50.75</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7075,10 +7051,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.884</v>
+        <v>0.593</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.872</v>
+        <v>0.611</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7091,28 +7067,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>3.01</v>
+        <v>0.525</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>0.0033</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>3468000</v>
+        <v>3369900</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>1.07</v>
+        <v>0.55</v>
       </c>
       <c r="H147" t="n">
-        <v>49.45</v>
+        <v>52.8</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7120,10 +7096,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>3.013</v>
+        <v>0.518</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>3.041</v>
+        <v>0.53</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7136,28 +7112,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.525</v>
+        <v>0.885</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>3369900</v>
+        <v>3343400</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.55</v>
+        <v>3.1</v>
       </c>
       <c r="H148" t="n">
-        <v>52.8</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7165,10 +7141,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.518</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.53</v>
+        <v>0.793</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7181,28 +7157,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.885</v>
+        <v>0.265</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>3343400</v>
+        <v>3341500</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="H149" t="n">
-        <v>72.20999999999999</v>
+        <v>54.05</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7210,10 +7186,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.793</v>
+        <v>0.273</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7226,39 +7202,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.265</v>
+        <v>0.615</v>
       </c>
       <c r="E150" s="17" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>3341500</v>
+        <v>3299500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="H150" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.253</v>
+        <v>0.608</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.273</v>
+        <v>0.587</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7271,39 +7247,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.615</v>
+        <v>0.55</v>
       </c>
       <c r="E151" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>3299500</v>
+        <v>3286800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="H151" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.26</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.608</v>
+        <v>0.493</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.587</v>
+        <v>0.395</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
